--- a/s60_signal/position-01398-601398.xlsx
+++ b/s60_signal/position-01398-601398.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5007" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5010" uniqueCount="499">
   <si>
     <t>trade_time</t>
   </si>
@@ -631,7 +631,7 @@
     <t>2021-08-16</t>
   </si>
   <si>
-    <t>2021-08-13</t>
+    <t>2021-08-12</t>
   </si>
   <si>
     <t>2017-05-12</t>
@@ -1504,7 +1504,7 @@
     <t>2021-08-10</t>
   </si>
   <si>
-    <t>2021-08-12</t>
+    <t>2021-08-13</t>
   </si>
   <si>
     <t>2021-08-17</t>
@@ -1868,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1665"/>
+  <dimension ref="A1:P1666"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -82073,10 +82073,10 @@
         <v>0</v>
       </c>
       <c r="B1605" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C1605">
-        <v>2.327681500351852</v>
+        <v>2.352560950813493</v>
       </c>
       <c r="D1605" t="s">
         <v>200</v>
@@ -82088,22 +82088,22 @@
         <v>1</v>
       </c>
       <c r="G1605">
-        <v>0.006772318499648147</v>
+        <v>0.006807439049186507</v>
       </c>
       <c r="H1605">
         <v>0.006917921247339947</v>
       </c>
       <c r="I1605">
-        <v>0.09439725230820128</v>
+        <v>0.06951780184656053</v>
       </c>
       <c r="J1605">
         <v>0.5120549538359788</v>
       </c>
       <c r="K1605">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="L1605">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="M1605">
         <v>4.39</v>
@@ -83673,10 +83673,10 @@
         <v>3</v>
       </c>
       <c r="B1637" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C1637">
-        <v>2.169622737055323</v>
+        <v>2.170960881124193</v>
       </c>
       <c r="D1637" t="s">
         <v>339</v>
@@ -83688,22 +83688,22 @@
         <v>-1</v>
       </c>
       <c r="G1637">
-        <v>0.007090377262944676</v>
+        <v>0.007069039118875807</v>
       </c>
       <c r="H1637">
         <v>0.007040377262944677</v>
       </c>
       <c r="I1637">
-        <v>0.04999999999999982</v>
+        <v>0.05133814406886916</v>
       </c>
       <c r="J1637">
         <v>0.5669072034434739</v>
       </c>
       <c r="K1637">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="L1637">
-        <v>4.63</v>
+        <v>4.62</v>
       </c>
       <c r="M1637">
         <v>4.34</v>
@@ -84576,7 +84576,7 @@
         <v>205</v>
       </c>
       <c r="C1655">
-        <v>1.883252760897444</v>
+        <v>1.884533672299485</v>
       </c>
       <c r="D1655" t="s">
         <v>200</v>
@@ -84588,22 +84588,22 @@
         <v>1</v>
       </c>
       <c r="G1655">
-        <v>0.007336747239102557</v>
+        <v>0.007375466327700515</v>
       </c>
       <c r="H1655">
         <v>0.007409226631501195</v>
       </c>
       <c r="I1655">
-        <v>0.04752060760136123</v>
+        <v>0.04623969619931989</v>
       </c>
       <c r="J1655">
         <v>0.6239696199319351</v>
       </c>
       <c r="K1655">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="L1655">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="M1655">
         <v>4.39</v>
@@ -84765,7 +84765,7 @@
         <v>1</v>
       </c>
       <c r="P1658" t="s">
-        <v>496</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1659" spans="1:16">
@@ -84815,7 +84815,7 @@
         <v>1</v>
       </c>
       <c r="P1659" t="s">
-        <v>496</v>
+        <v>205</v>
       </c>
     </row>
     <row r="1660" spans="1:16">
@@ -84865,57 +84865,57 @@
         <v>1</v>
       </c>
       <c r="P1660" t="s">
-        <v>205</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1661" spans="1:16">
       <c r="A1661" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1661" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C1661">
-        <v>1.895738971054095</v>
+        <v>1.898673265036768</v>
       </c>
       <c r="D1661" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E1661">
-        <v>1.84667510188895</v>
+        <v>1.838673265036769</v>
       </c>
       <c r="F1661">
         <v>-1</v>
       </c>
       <c r="G1661">
-        <v>0.007424261028945905</v>
+        <v>0.007381326734963231</v>
       </c>
       <c r="H1661">
-        <v>0.00741332489811105</v>
+        <v>0.007321326734963232</v>
       </c>
       <c r="I1661">
-        <v>0.0490638691651446</v>
+        <v>0.05999999999999961</v>
       </c>
       <c r="J1661">
-        <v>0.6354623055048059</v>
+        <v>0.6316421048302377</v>
       </c>
       <c r="K1661">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="L1661">
-        <v>4.66</v>
+        <v>4.64</v>
       </c>
       <c r="M1661">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="N1661">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="O1661">
         <v>1</v>
       </c>
       <c r="P1661" t="s">
-        <v>204</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1662" spans="1:16">
@@ -84926,28 +84926,28 @@
         <v>199</v>
       </c>
       <c r="C1662">
-        <v>1.877866882646975</v>
+        <v>1.895738971054095</v>
       </c>
       <c r="D1662" t="s">
         <v>337</v>
       </c>
       <c r="E1662">
-        <v>1.828679757699712</v>
+        <v>1.84667510188895</v>
       </c>
       <c r="F1662">
         <v>-1</v>
       </c>
       <c r="G1662">
-        <v>0.007442133117353025</v>
+        <v>0.007424261028945905</v>
       </c>
       <c r="H1662">
-        <v>0.007431320242300288</v>
+        <v>0.00741332489811105</v>
       </c>
       <c r="I1662">
-        <v>0.04918712494726263</v>
+        <v>0.0490638691651446</v>
       </c>
       <c r="J1662">
-        <v>0.6395708315754082</v>
+        <v>0.6354623055048059</v>
       </c>
       <c r="K1662">
         <v>4.35</v>
@@ -84965,7 +84965,7 @@
         <v>1</v>
       </c>
       <c r="P1662" t="s">
-        <v>497</v>
+        <v>204</v>
       </c>
     </row>
     <row r="1663" spans="1:16">
@@ -84976,28 +84976,28 @@
         <v>199</v>
       </c>
       <c r="C1663">
-        <v>1.86003580922007</v>
+        <v>1.877866882646975</v>
       </c>
       <c r="D1663" t="s">
         <v>337</v>
       </c>
       <c r="E1663">
-        <v>1.810725711352622</v>
+        <v>1.828679757699712</v>
       </c>
       <c r="F1663">
         <v>-1</v>
       </c>
       <c r="G1663">
-        <v>0.00745996419077993</v>
+        <v>0.007442133117353025</v>
       </c>
       <c r="H1663">
-        <v>0.007449274288647378</v>
+        <v>0.007431320242300288</v>
       </c>
       <c r="I1663">
-        <v>0.04931009786744855</v>
+        <v>0.04918712494726263</v>
       </c>
       <c r="J1663">
-        <v>0.6436699289149265</v>
+        <v>0.6395708315754082</v>
       </c>
       <c r="K1663">
         <v>4.35</v>
@@ -85015,7 +85015,7 @@
         <v>1</v>
       </c>
       <c r="P1663" t="s">
-        <v>200</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1664" spans="1:16">
@@ -85026,28 +85026,28 @@
         <v>199</v>
       </c>
       <c r="C1664">
-        <v>1.847657820345777</v>
+        <v>1.86003580922007</v>
       </c>
       <c r="D1664" t="s">
         <v>337</v>
       </c>
       <c r="E1664">
-        <v>1.798262357037816</v>
+        <v>1.810725711352622</v>
       </c>
       <c r="F1664">
         <v>-1</v>
       </c>
       <c r="G1664">
-        <v>0.007472342179654224</v>
+        <v>0.00745996419077993</v>
       </c>
       <c r="H1664">
-        <v>0.007461737642962185</v>
+        <v>0.007449274288647378</v>
       </c>
       <c r="I1664">
-        <v>0.04939546330796096</v>
+        <v>0.04931009786744855</v>
       </c>
       <c r="J1664">
-        <v>0.6465154435986722</v>
+        <v>0.6436699289149265</v>
       </c>
       <c r="K1664">
         <v>4.35</v>
@@ -85065,7 +85065,7 @@
         <v>1</v>
       </c>
       <c r="P1664" t="s">
-        <v>498</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1665" spans="1:16">
@@ -85073,48 +85073,98 @@
         <v>0</v>
       </c>
       <c r="B1665" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C1665">
-        <v>1.803294242996774</v>
+        <v>1.847657820345777</v>
       </c>
       <c r="D1665" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E1665">
-        <v>1.743294242996775</v>
+        <v>1.798262357037816</v>
       </c>
       <c r="F1665">
         <v>-1</v>
       </c>
       <c r="G1665">
+        <v>0.007472342179654224</v>
+      </c>
+      <c r="H1665">
+        <v>0.007461737642962185</v>
+      </c>
+      <c r="I1665">
+        <v>0.04939546330796096</v>
+      </c>
+      <c r="J1665">
+        <v>0.6465154435986722</v>
+      </c>
+      <c r="K1665">
+        <v>4.35</v>
+      </c>
+      <c r="L1665">
+        <v>4.66</v>
+      </c>
+      <c r="M1665">
+        <v>4.38</v>
+      </c>
+      <c r="N1665">
+        <v>4.63</v>
+      </c>
+      <c r="O1665">
+        <v>1</v>
+      </c>
+      <c r="P1665" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:16">
+      <c r="A1666" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1666">
+        <v>1.803294242996774</v>
+      </c>
+      <c r="D1666" t="s">
+        <v>339</v>
+      </c>
+      <c r="E1666">
+        <v>1.743294242996775</v>
+      </c>
+      <c r="F1666">
+        <v>-1</v>
+      </c>
+      <c r="G1666">
         <v>0.007476705757003226</v>
       </c>
-      <c r="H1665">
+      <c r="H1666">
         <v>0.007416705757003225</v>
       </c>
-      <c r="I1665">
+      <c r="I1666">
         <v>0.05999999999999961</v>
       </c>
-      <c r="J1665">
+      <c r="J1666">
         <v>0.6536188380191763</v>
       </c>
-      <c r="K1665">
+      <c r="K1666">
         <v>4.34</v>
       </c>
-      <c r="L1665">
+      <c r="L1666">
         <v>4.64</v>
       </c>
-      <c r="M1665">
+      <c r="M1666">
         <v>4.34</v>
       </c>
-      <c r="N1665">
+      <c r="N1666">
         <v>4.58</v>
       </c>
-      <c r="O1665">
-        <v>1</v>
-      </c>
-      <c r="P1665" t="s">
+      <c r="O1666">
+        <v>1</v>
+      </c>
+      <c r="P1666" t="s">
         <v>337</v>
       </c>
     </row>

--- a/s60_signal/position-01398-601398.xlsx
+++ b/s60_signal/position-01398-601398.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5100" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5106" uniqueCount="512">
   <si>
     <t>trade_time</t>
   </si>
@@ -1024,7 +1024,7 @@
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-09-16</t>
+    <t>2021-09-17</t>
   </si>
   <si>
     <t>2021-08-18</t>
@@ -1548,6 +1548,9 @@
   <si>
     <t>2021-09-10</t>
   </si>
+  <si>
+    <t>2021-09-13</t>
+  </si>
 </sst>
 </file>
 
@@ -1904,7 +1907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1696"/>
+  <dimension ref="A1:P1698"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -81568,7 +81571,7 @@
         <v>336</v>
       </c>
       <c r="E1594">
-        <v>2.847085918051282</v>
+        <v>2.875493780812515</v>
       </c>
       <c r="F1594">
         <v>-1</v>
@@ -81577,10 +81580,10 @@
         <v>0.006636545532993648</v>
       </c>
       <c r="H1594">
-        <v>0.006512914081948719</v>
+        <v>0.006524506219187486</v>
       </c>
       <c r="I1594">
-        <v>0.05636854895506938</v>
+        <v>0.02796068619383618</v>
       </c>
       <c r="J1594">
         <v>0.4203931380616326</v>
@@ -81592,10 +81595,10 @@
         <v>4.77</v>
       </c>
       <c r="M1594">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1594">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1594">
         <v>1</v>
@@ -81615,10 +81618,10 @@
         <v>2.722377288297685</v>
       </c>
       <c r="D1595" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E1595">
-        <v>2.797963212500413</v>
+        <v>2.805020495302232</v>
       </c>
       <c r="F1595">
         <v>1</v>
@@ -81627,10 +81630,10 @@
         <v>0.006517622711702315</v>
       </c>
       <c r="H1595">
-        <v>0.006542036787499587</v>
+        <v>0.006514979504697769</v>
       </c>
       <c r="I1595">
-        <v>0.07558592420272792</v>
+        <v>0.08264320700454642</v>
       </c>
       <c r="J1595">
         <v>0.4264320700454641</v>
@@ -81642,10 +81645,10 @@
         <v>4.62</v>
       </c>
       <c r="M1595">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="N1595">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="O1595">
         <v>1</v>
@@ -81665,10 +81668,10 @@
         <v>2.725020495302231</v>
       </c>
       <c r="D1596" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E1596">
-        <v>2.797963212500413</v>
+        <v>2.805020495302232</v>
       </c>
       <c r="F1596">
         <v>1</v>
@@ -81677,10 +81680,10 @@
         <v>0.006434979504697768</v>
       </c>
       <c r="H1596">
-        <v>0.006542036787499587</v>
+        <v>0.006514979504697769</v>
       </c>
       <c r="I1596">
-        <v>0.07294271719818157</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="J1596">
         <v>0.4264320700454641</v>
@@ -81692,10 +81695,10 @@
         <v>4.58</v>
       </c>
       <c r="M1596">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="N1596">
-        <v>4.67</v>
+        <v>4.66</v>
       </c>
       <c r="O1596">
         <v>1</v>
@@ -81768,7 +81771,7 @@
         <v>336</v>
       </c>
       <c r="E1598">
-        <v>2.820756174601776</v>
+        <v>2.849284816002686</v>
       </c>
       <c r="F1598">
         <v>-1</v>
@@ -81777,10 +81780,10 @@
         <v>0.006663358391001861</v>
       </c>
       <c r="H1598">
-        <v>0.006539243825398224</v>
+        <v>0.006550715183997313</v>
       </c>
       <c r="I1598">
-        <v>0.05588543439636284</v>
+        <v>0.02735679299545257</v>
       </c>
       <c r="J1598">
         <v>0.4264320700454641</v>
@@ -81792,10 +81795,10 @@
         <v>4.77</v>
       </c>
       <c r="M1598">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1598">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1598">
         <v>1</v>
@@ -81968,7 +81971,7 @@
         <v>336</v>
       </c>
       <c r="E1602">
-        <v>2.78814831662695</v>
+        <v>2.816826535358019</v>
       </c>
       <c r="F1602">
         <v>-1</v>
@@ -81977,10 +81980,10 @@
         <v>0.006643547230200724</v>
       </c>
       <c r="H1602">
-        <v>0.006571851683373049</v>
+        <v>0.006583173464641981</v>
       </c>
       <c r="I1602">
-        <v>0.02830445317232799</v>
+        <v>-0.0003737655587414679</v>
       </c>
       <c r="J1602">
         <v>0.4339109365534518</v>
@@ -81992,10 +81995,10 @@
         <v>4.73</v>
       </c>
       <c r="M1602">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1602">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1602">
         <v>1</v>
@@ -82009,43 +82012,43 @@
         <v>4</v>
       </c>
       <c r="B1603" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C1603">
-        <v>2.814757222971605</v>
+        <v>2.843435441702673</v>
       </c>
       <c r="D1603" t="s">
         <v>336</v>
       </c>
       <c r="E1603">
-        <v>2.78814831662695</v>
+        <v>2.816826535358019</v>
       </c>
       <c r="F1603">
         <v>-1</v>
       </c>
       <c r="G1603">
-        <v>0.006685242777028395</v>
+        <v>0.006696564558297326</v>
       </c>
       <c r="H1603">
-        <v>0.006571851683373049</v>
+        <v>0.006583173464641981</v>
       </c>
       <c r="I1603">
-        <v>0.02660890634465529</v>
+        <v>0.02660890634465396</v>
       </c>
       <c r="J1603">
         <v>0.4339109365534518</v>
       </c>
       <c r="K1603">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="L1603">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="M1603">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1603">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1603">
         <v>1</v>
@@ -82168,7 +82171,7 @@
         <v>336</v>
       </c>
       <c r="E1606">
-        <v>2.74706503924229</v>
+        <v>2.775931713374207</v>
       </c>
       <c r="F1606">
         <v>-1</v>
@@ -82177,10 +82180,10 @@
         <v>0.0066851016460875</v>
       </c>
       <c r="H1606">
-        <v>0.00661293496075771</v>
+        <v>0.006624068286625794</v>
       </c>
       <c r="I1606">
-        <v>0.027833314670211</v>
+        <v>-0.00103335946170624</v>
       </c>
       <c r="J1606">
         <v>0.443333706595805</v>
@@ -82192,10 +82195,10 @@
         <v>4.73</v>
       </c>
       <c r="M1606">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1606">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1606">
         <v>1</v>
@@ -82218,7 +82221,7 @@
         <v>336</v>
       </c>
       <c r="E1607">
-        <v>2.74706503924229</v>
+        <v>2.775931713374207</v>
       </c>
       <c r="F1607">
         <v>-1</v>
@@ -82227,10 +82230,10 @@
         <v>0.006727268331417291</v>
       </c>
       <c r="H1607">
-        <v>0.00661293496075771</v>
+        <v>0.006624068286625794</v>
       </c>
       <c r="I1607">
-        <v>0.02566662934041997</v>
+        <v>-0.00320004479149727</v>
       </c>
       <c r="J1607">
         <v>0.443333706595805</v>
@@ -82242,10 +82245,10 @@
         <v>4.75</v>
       </c>
       <c r="M1607">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1607">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1607">
         <v>1</v>
@@ -82309,40 +82312,40 @@
         <v>1</v>
       </c>
       <c r="B1609" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C1609">
-        <v>2.72128645686155</v>
+        <v>2.603170798816128</v>
       </c>
       <c r="D1609" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E1609">
-        <v>2.694060986829105</v>
+        <v>2.684951174842083</v>
       </c>
       <c r="F1609">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1609">
-        <v>0.00673871354313845</v>
+        <v>0.006556829201183872</v>
       </c>
       <c r="H1609">
-        <v>0.006665939013170895</v>
+        <v>0.006675048825157917</v>
       </c>
       <c r="I1609">
-        <v>0.02722547003244502</v>
+        <v>0.08178037602595456</v>
       </c>
       <c r="J1609">
         <v>0.4554905993511226</v>
       </c>
       <c r="K1609">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="L1609">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1609">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="N1609">
         <v>4.68</v>
@@ -82359,43 +82362,43 @@
         <v>2</v>
       </c>
       <c r="B1610" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1610">
-        <v>2.718511926893993</v>
+        <v>2.72128645686155</v>
       </c>
       <c r="D1610" t="s">
         <v>336</v>
       </c>
       <c r="E1610">
-        <v>2.694060986829105</v>
+        <v>2.723170798816128</v>
       </c>
       <c r="F1610">
         <v>-1</v>
       </c>
       <c r="G1610">
-        <v>0.006781488073106006</v>
+        <v>0.00673871354313845</v>
       </c>
       <c r="H1610">
-        <v>0.006665939013170895</v>
+        <v>0.006676829201183872</v>
       </c>
       <c r="I1610">
-        <v>0.02445094006488846</v>
+        <v>-0.001884341954578428</v>
       </c>
       <c r="J1610">
         <v>0.4554905993511226</v>
       </c>
       <c r="K1610">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1610">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1610">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1610">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1610">
         <v>1</v>
@@ -82406,96 +82409,96 @@
     </row>
     <row r="1611" spans="1:16">
       <c r="A1611" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1611" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1611">
-        <v>2.541550734673264</v>
+        <v>2.718511926893993</v>
       </c>
       <c r="D1611" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1611">
-        <v>2.612806373612788</v>
+        <v>2.723170798816128</v>
       </c>
       <c r="F1611">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1611">
-        <v>0.006618449265326736</v>
+        <v>0.006781488073106006</v>
       </c>
       <c r="H1611">
-        <v>0.006727193626387212</v>
+        <v>0.006676829201183872</v>
       </c>
       <c r="I1611">
-        <v>0.07125563893952425</v>
+        <v>-0.004658871922134988</v>
       </c>
       <c r="J1611">
-        <v>0.4686090265118935</v>
+        <v>0.4554905993511226</v>
       </c>
       <c r="K1611">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1611">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1611">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1611">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1611">
         <v>1</v>
       </c>
       <c r="P1611" t="s">
-        <v>330</v>
+        <v>193</v>
       </c>
     </row>
     <row r="1612" spans="1:16">
       <c r="A1612" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1612" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1612">
-        <v>2.66343419308255</v>
+        <v>2.541550734673264</v>
       </c>
       <c r="D1612" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1612">
-        <v>2.636864644408144</v>
+        <v>2.612806373612788</v>
       </c>
       <c r="F1612">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1612">
-        <v>0.006796565806917451</v>
+        <v>0.006618449265326736</v>
       </c>
       <c r="H1612">
-        <v>0.006723135355591855</v>
+        <v>0.006727193626387212</v>
       </c>
       <c r="I1612">
-        <v>0.0265695486744062</v>
+        <v>0.07125563893952425</v>
       </c>
       <c r="J1612">
         <v>0.4686090265118935</v>
       </c>
       <c r="K1612">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1612">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1612">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1612">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1612">
         <v>1</v>
@@ -82506,46 +82509,46 @@
     </row>
     <row r="1613" spans="1:16">
       <c r="A1613" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1613" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1613">
-        <v>2.660003741756955</v>
+        <v>2.66343419308255</v>
       </c>
       <c r="D1613" t="s">
         <v>336</v>
       </c>
       <c r="E1613">
-        <v>2.636864644408144</v>
+        <v>2.666236824938383</v>
       </c>
       <c r="F1613">
         <v>-1</v>
       </c>
       <c r="G1613">
-        <v>0.006839996258243045</v>
+        <v>0.006796565806917451</v>
       </c>
       <c r="H1613">
-        <v>0.006723135355591855</v>
+        <v>0.006733763175061618</v>
       </c>
       <c r="I1613">
-        <v>0.02313909734881126</v>
+        <v>-0.002802631855832516</v>
       </c>
       <c r="J1613">
         <v>0.4686090265118935</v>
       </c>
       <c r="K1613">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1613">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1613">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1613">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1613">
         <v>1</v>
@@ -82556,96 +82559,96 @@
     </row>
     <row r="1614" spans="1:16">
       <c r="A1614" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1614" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1614">
-        <v>2.477037976734704</v>
+        <v>2.660003741756955</v>
       </c>
       <c r="D1614" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1614">
-        <v>2.547700394911575</v>
+        <v>2.666236824938383</v>
       </c>
       <c r="F1614">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1614">
-        <v>0.006682962023265297</v>
+        <v>0.006839996258243045</v>
       </c>
       <c r="H1614">
-        <v>0.006792299605088425</v>
+        <v>0.006733763175061618</v>
       </c>
       <c r="I1614">
-        <v>0.07066241817687091</v>
+        <v>-0.006233083181427457</v>
       </c>
       <c r="J1614">
-        <v>0.483439545578229</v>
+        <v>0.4686090265118935</v>
       </c>
       <c r="K1614">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1614">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1614">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1614">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1614">
         <v>1</v>
       </c>
       <c r="P1614" t="s">
-        <v>485</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1615" spans="1:16">
       <c r="A1615" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1615" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1615">
-        <v>2.598031604000011</v>
+        <v>2.477037976734704</v>
       </c>
       <c r="D1615" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1615">
-        <v>2.572203581278921</v>
+        <v>2.547700394911575</v>
       </c>
       <c r="F1615">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1615">
-        <v>0.00686196839599999</v>
+        <v>0.006682962023265297</v>
       </c>
       <c r="H1615">
-        <v>0.006787796418721078</v>
+        <v>0.006792299605088425</v>
       </c>
       <c r="I1615">
-        <v>0.02582802272108964</v>
+        <v>0.07066241817687091</v>
       </c>
       <c r="J1615">
         <v>0.483439545578229</v>
       </c>
       <c r="K1615">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1615">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1615">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1615">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1615">
         <v>1</v>
@@ -82656,46 +82659,46 @@
     </row>
     <row r="1616" spans="1:16">
       <c r="A1616" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1616" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1616">
-        <v>2.593859626721099</v>
+        <v>2.598031604000011</v>
       </c>
       <c r="D1616" t="s">
         <v>336</v>
       </c>
       <c r="E1616">
-        <v>2.572203581278921</v>
+        <v>2.601872372190487</v>
       </c>
       <c r="F1616">
         <v>-1</v>
       </c>
       <c r="G1616">
-        <v>0.006906140373278902</v>
+        <v>0.00686196839599999</v>
       </c>
       <c r="H1616">
-        <v>0.006787796418721078</v>
+        <v>0.006798127627809514</v>
       </c>
       <c r="I1616">
-        <v>0.0216560454421777</v>
+        <v>-0.003840768190475963</v>
       </c>
       <c r="J1616">
         <v>0.483439545578229</v>
       </c>
       <c r="K1616">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1616">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1616">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1616">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1616">
         <v>1</v>
@@ -82706,96 +82709,96 @@
     </row>
     <row r="1617" spans="1:16">
       <c r="A1617" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1617" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1617">
-        <v>2.433339935830427</v>
+        <v>2.593859626721099</v>
       </c>
       <c r="D1617" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1617">
-        <v>2.503600532941511</v>
+        <v>2.601872372190487</v>
       </c>
       <c r="F1617">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1617">
-        <v>0.006726660064169574</v>
+        <v>0.006906140373278902</v>
       </c>
       <c r="H1617">
-        <v>0.006836399467058489</v>
+        <v>0.006798127627809514</v>
       </c>
       <c r="I1617">
-        <v>0.07026059711108434</v>
+        <v>-0.008012745469387905</v>
       </c>
       <c r="J1617">
-        <v>0.4934850722228905</v>
+        <v>0.483439545578229</v>
       </c>
       <c r="K1617">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1617">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1617">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1617">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1617">
         <v>1</v>
       </c>
       <c r="P1617" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="1618" spans="1:16">
       <c r="A1618" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1618" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1618">
-        <v>2.553730831497053</v>
+        <v>2.433339935830427</v>
       </c>
       <c r="D1618" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1618">
-        <v>2.528405085108197</v>
+        <v>2.503600532941511</v>
       </c>
       <c r="F1618">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1618">
-        <v>0.006906269168502947</v>
+        <v>0.006726660064169574</v>
       </c>
       <c r="H1618">
-        <v>0.006831594914891803</v>
+        <v>0.006836399467058489</v>
       </c>
       <c r="I1618">
-        <v>0.02532574638885654</v>
+        <v>0.07026059711108434</v>
       </c>
       <c r="J1618">
         <v>0.4934850722228905</v>
       </c>
       <c r="K1618">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1618">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1618">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1618">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1618">
         <v>1</v>
@@ -82806,46 +82809,46 @@
     </row>
     <row r="1619" spans="1:16">
       <c r="A1619" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1619" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1619">
-        <v>2.549056577885908</v>
+        <v>2.553730831497053</v>
       </c>
       <c r="D1619" t="s">
         <v>336</v>
       </c>
       <c r="E1619">
-        <v>2.528405085108197</v>
+        <v>2.558274786552655</v>
       </c>
       <c r="F1619">
         <v>-1</v>
       </c>
       <c r="G1619">
-        <v>0.006950943422114092</v>
+        <v>0.006906269168502947</v>
       </c>
       <c r="H1619">
-        <v>0.006831594914891803</v>
+        <v>0.006841725213447346</v>
       </c>
       <c r="I1619">
-        <v>0.0206514927777115</v>
+        <v>-0.004543955055602122</v>
       </c>
       <c r="J1619">
         <v>0.4934850722228905</v>
       </c>
       <c r="K1619">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1619">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1619">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1619">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1619">
         <v>1</v>
@@ -82856,96 +82859,96 @@
     </row>
     <row r="1620" spans="1:16">
       <c r="A1620" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1620" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1620">
-        <v>2.395841588621165</v>
+        <v>2.549056577885908</v>
       </c>
       <c r="D1620" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1620">
-        <v>2.465757373344118</v>
+        <v>2.558274786552655</v>
       </c>
       <c r="F1620">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1620">
-        <v>0.006764158411378836</v>
+        <v>0.006950943422114092</v>
       </c>
       <c r="H1620">
-        <v>0.006874242626655882</v>
+        <v>0.006841725213447346</v>
       </c>
       <c r="I1620">
-        <v>0.06991578472295279</v>
+        <v>-0.009218208666747163</v>
       </c>
       <c r="J1620">
-        <v>0.5021053819261689</v>
+        <v>0.4934850722228905</v>
       </c>
       <c r="K1620">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1620">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1620">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1620">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1620">
         <v>1</v>
       </c>
       <c r="P1620" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="1621" spans="1:16">
       <c r="A1621" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1621" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1621">
-        <v>2.515715265705595</v>
+        <v>2.395841588621165</v>
       </c>
       <c r="D1621" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1621">
-        <v>2.490820534801903</v>
+        <v>2.465757373344118</v>
       </c>
       <c r="F1621">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1621">
-        <v>0.006944284734294406</v>
+        <v>0.006764158411378836</v>
       </c>
       <c r="H1621">
-        <v>0.006869179465198096</v>
+        <v>0.006874242626655882</v>
       </c>
       <c r="I1621">
-        <v>0.02489473090369243</v>
+        <v>0.06991578472295279</v>
       </c>
       <c r="J1621">
         <v>0.5021053819261689</v>
       </c>
       <c r="K1621">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1621">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1621">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1621">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1621">
         <v>1</v>
@@ -82956,46 +82959,46 @@
     </row>
     <row r="1622" spans="1:16">
       <c r="A1622" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1622" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1622">
-        <v>2.510609996609287</v>
+        <v>2.515715265705595</v>
       </c>
       <c r="D1622" t="s">
         <v>336</v>
       </c>
       <c r="E1622">
-        <v>2.490820534801903</v>
+        <v>2.520862642440427</v>
       </c>
       <c r="F1622">
         <v>-1</v>
       </c>
       <c r="G1622">
-        <v>0.006989390003390714</v>
+        <v>0.006944284734294406</v>
       </c>
       <c r="H1622">
-        <v>0.006869179465198096</v>
+        <v>0.006879137357559574</v>
       </c>
       <c r="I1622">
-        <v>0.01978946180738372</v>
+        <v>-0.005147376734831788</v>
       </c>
       <c r="J1622">
         <v>0.5021053819261689</v>
       </c>
       <c r="K1622">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1622">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1622">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1622">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1622">
         <v>1</v>
@@ -83006,96 +83009,96 @@
     </row>
     <row r="1623" spans="1:16">
       <c r="A1623" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1623" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1623">
-        <v>2.352560950813493</v>
+        <v>2.510609996609287</v>
       </c>
       <c r="D1623" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1623">
-        <v>2.422078752660053</v>
+        <v>2.520862642440427</v>
       </c>
       <c r="F1623">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1623">
-        <v>0.006807439049186507</v>
+        <v>0.006989390003390714</v>
       </c>
       <c r="H1623">
-        <v>0.006917921247339947</v>
+        <v>0.006879137357559574</v>
       </c>
       <c r="I1623">
-        <v>0.06951780184656053</v>
+        <v>-0.01025264583114049</v>
       </c>
       <c r="J1623">
-        <v>0.5120549538359788</v>
+        <v>0.5021053819261689</v>
       </c>
       <c r="K1623">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1623">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1623">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1623">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1623">
         <v>1</v>
       </c>
       <c r="P1623" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="1624" spans="1:16">
       <c r="A1624" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1624" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1624">
-        <v>2.471837653583334</v>
+        <v>2.352560950813493</v>
       </c>
       <c r="D1624" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1624">
-        <v>2.447440401275132</v>
+        <v>2.422078752660053</v>
       </c>
       <c r="F1624">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1624">
-        <v>0.006988162346416667</v>
+        <v>0.006807439049186507</v>
       </c>
       <c r="H1624">
-        <v>0.006912559598724867</v>
+        <v>0.006917921247339947</v>
       </c>
       <c r="I1624">
-        <v>0.02439725230820189</v>
+        <v>0.06951780184656053</v>
       </c>
       <c r="J1624">
         <v>0.5120549538359788</v>
       </c>
       <c r="K1624">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1624">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1624">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1624">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1624">
         <v>1</v>
@@ -83106,46 +83109,46 @@
     </row>
     <row r="1625" spans="1:16">
       <c r="A1625" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1625" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1625">
-        <v>2.466234905891535</v>
+        <v>2.471837653583334</v>
       </c>
       <c r="D1625" t="s">
         <v>336</v>
       </c>
       <c r="E1625">
-        <v>2.447440401275132</v>
+        <v>2.477681500351852</v>
       </c>
       <c r="F1625">
         <v>-1</v>
       </c>
       <c r="G1625">
-        <v>0.007033765094108466</v>
+        <v>0.006988162346416667</v>
       </c>
       <c r="H1625">
-        <v>0.006912559598724867</v>
+        <v>0.006922318499648148</v>
       </c>
       <c r="I1625">
-        <v>0.01879450461640264</v>
+        <v>-0.005843846768518457</v>
       </c>
       <c r="J1625">
         <v>0.5120549538359788</v>
       </c>
       <c r="K1625">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1625">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1625">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1625">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1625">
         <v>1</v>
@@ -83156,96 +83159,96 @@
     </row>
     <row r="1626" spans="1:16">
       <c r="A1626" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1626" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1626">
-        <v>2.316817307845334</v>
+        <v>2.466234905891535</v>
       </c>
       <c r="D1626" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1626">
-        <v>2.386006432515176</v>
+        <v>2.477681500351852</v>
       </c>
       <c r="F1626">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1626">
-        <v>0.006843182692154667</v>
+        <v>0.007033765094108466</v>
       </c>
       <c r="H1626">
-        <v>0.006953993567484824</v>
+        <v>0.006922318499648148</v>
       </c>
       <c r="I1626">
-        <v>0.06918912466984217</v>
+        <v>-0.0114465944603177</v>
       </c>
       <c r="J1626">
-        <v>0.5202718832539462</v>
+        <v>0.5120549538359788</v>
       </c>
       <c r="K1626">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1626">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1626">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1626">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1626">
         <v>1</v>
       </c>
       <c r="P1626" t="s">
-        <v>331</v>
+        <v>488</v>
       </c>
     </row>
     <row r="1627" spans="1:16">
       <c r="A1627" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1627" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1627">
-        <v>2.435600994850097</v>
+        <v>2.316817307845334</v>
       </c>
       <c r="D1627" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1627">
-        <v>2.411614589012794</v>
+        <v>2.386006432515176</v>
       </c>
       <c r="F1627">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1627">
-        <v>0.007024399005149904</v>
+        <v>0.006843182692154667</v>
       </c>
       <c r="H1627">
-        <v>0.006948385410987206</v>
+        <v>0.006953993567484824</v>
       </c>
       <c r="I1627">
-        <v>0.0239864058373036</v>
+        <v>0.06918912466984217</v>
       </c>
       <c r="J1627">
         <v>0.5202718832539462</v>
       </c>
       <c r="K1627">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1627">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1627">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1627">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1627">
         <v>1</v>
@@ -83256,46 +83259,46 @@
     </row>
     <row r="1628" spans="1:16">
       <c r="A1628" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1628" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1628">
-        <v>2.4295874006874</v>
+        <v>2.435600994850097</v>
       </c>
       <c r="D1628" t="s">
         <v>336</v>
       </c>
       <c r="E1628">
-        <v>2.411614589012794</v>
+        <v>2.442020026677874</v>
       </c>
       <c r="F1628">
         <v>-1</v>
       </c>
       <c r="G1628">
-        <v>0.0070704125993126</v>
+        <v>0.007024399005149904</v>
       </c>
       <c r="H1628">
-        <v>0.006948385410987206</v>
+        <v>0.006957979973322127</v>
       </c>
       <c r="I1628">
-        <v>0.01797281167460607</v>
+        <v>-0.006419031827776145</v>
       </c>
       <c r="J1628">
         <v>0.5202718832539462</v>
       </c>
       <c r="K1628">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1628">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1628">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1628">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1628">
         <v>1</v>
@@ -83306,96 +83309,96 @@
     </row>
     <row r="1629" spans="1:16">
       <c r="A1629" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1629" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1629">
-        <v>2.288262168048912</v>
+        <v>2.4295874006874</v>
       </c>
       <c r="D1629" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1629">
-        <v>2.357188716720625</v>
+        <v>2.442020026677874</v>
       </c>
       <c r="F1629">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1629">
-        <v>0.006871737831951089</v>
+        <v>0.0070704125993126</v>
       </c>
       <c r="H1629">
-        <v>0.006982811283279375</v>
+        <v>0.006957979973322127</v>
       </c>
       <c r="I1629">
-        <v>0.06892654867171366</v>
+        <v>-0.01243262599047368</v>
       </c>
       <c r="J1629">
-        <v>0.5268362832071468</v>
+        <v>0.5202718832539462</v>
       </c>
       <c r="K1629">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1629">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1629">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1629">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1629">
         <v>1</v>
       </c>
       <c r="P1629" t="s">
-        <v>489</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1630" spans="1:16">
       <c r="A1630" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1630" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1630">
-        <v>2.406651991056483</v>
+        <v>2.288262168048912</v>
       </c>
       <c r="D1630" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1630">
-        <v>2.382993805216839</v>
+        <v>2.357188716720625</v>
       </c>
       <c r="F1630">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1630">
-        <v>0.007053348008943518</v>
+        <v>0.006871737831951089</v>
       </c>
       <c r="H1630">
-        <v>0.00697700619478316</v>
+        <v>0.006982811283279375</v>
       </c>
       <c r="I1630">
-        <v>0.02365818583964341</v>
+        <v>0.06892654867171366</v>
       </c>
       <c r="J1630">
         <v>0.5268362832071468</v>
       </c>
       <c r="K1630">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1630">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1630">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1630">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1630">
         <v>1</v>
@@ -83406,46 +83409,46 @@
     </row>
     <row r="1631" spans="1:16">
       <c r="A1631" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1631" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1631">
-        <v>2.400310176896125</v>
+        <v>2.406651991056483</v>
       </c>
       <c r="D1631" t="s">
         <v>336</v>
       </c>
       <c r="E1631">
-        <v>2.382993805216839</v>
+        <v>2.413530530880983</v>
       </c>
       <c r="F1631">
         <v>-1</v>
       </c>
       <c r="G1631">
-        <v>0.007099689823103874</v>
+        <v>0.007053348008943518</v>
       </c>
       <c r="H1631">
-        <v>0.00697700619478316</v>
+        <v>0.006986469469119017</v>
       </c>
       <c r="I1631">
-        <v>0.01731637167928568</v>
+        <v>-0.006878539824500152</v>
       </c>
       <c r="J1631">
         <v>0.5268362832071468</v>
       </c>
       <c r="K1631">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1631">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1631">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1631">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1631">
         <v>1</v>
@@ -83456,96 +83459,96 @@
     </row>
     <row r="1632" spans="1:16">
       <c r="A1632" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1632" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1632">
-        <v>2.262985882191805</v>
+        <v>2.400310176896125</v>
       </c>
       <c r="D1632" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1632">
-        <v>2.331680005246443</v>
+        <v>2.413530530880983</v>
       </c>
       <c r="F1632">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1632">
-        <v>0.006897014117808195</v>
+        <v>0.007099689823103874</v>
       </c>
       <c r="H1632">
-        <v>0.007008319994753557</v>
+        <v>0.006986469469119017</v>
       </c>
       <c r="I1632">
-        <v>0.0686941230546374</v>
+        <v>-0.01322035398485788</v>
       </c>
       <c r="J1632">
-        <v>0.5326469236340677</v>
+        <v>0.5268362832071468</v>
       </c>
       <c r="K1632">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1632">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1632">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1632">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1632">
         <v>1</v>
       </c>
       <c r="P1632" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="1633" spans="1:16">
       <c r="A1633" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1633" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1633">
-        <v>2.381027066773762</v>
+        <v>2.262985882191805</v>
       </c>
       <c r="D1633" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1633">
-        <v>2.357659412955464</v>
+        <v>2.331680005246443</v>
       </c>
       <c r="F1633">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1633">
-        <v>0.00707897293322624</v>
+        <v>0.006897014117808195</v>
       </c>
       <c r="H1633">
-        <v>0.007002340587044536</v>
+        <v>0.007008319994753557</v>
       </c>
       <c r="I1633">
-        <v>0.02336765381829764</v>
+        <v>0.0686941230546374</v>
       </c>
       <c r="J1633">
         <v>0.5326469236340677</v>
       </c>
       <c r="K1633">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1633">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1633">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1633">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1633">
         <v>1</v>
@@ -83556,46 +83559,46 @@
     </row>
     <row r="1634" spans="1:16">
       <c r="A1634" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1634" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1634">
-        <v>2.374394720592058</v>
+        <v>2.381027066773762</v>
       </c>
       <c r="D1634" t="s">
         <v>336</v>
       </c>
       <c r="E1634">
-        <v>2.357659412955464</v>
+        <v>2.388312351428146</v>
       </c>
       <c r="F1634">
         <v>-1</v>
       </c>
       <c r="G1634">
-        <v>0.007125605279407942</v>
+        <v>0.00707897293322624</v>
       </c>
       <c r="H1634">
-        <v>0.007002340587044536</v>
+        <v>0.007011687648571854</v>
       </c>
       <c r="I1634">
-        <v>0.0167353076365937</v>
+        <v>-0.007285284654384494</v>
       </c>
       <c r="J1634">
         <v>0.5326469236340677</v>
       </c>
       <c r="K1634">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1634">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1634">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1634">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1634">
         <v>1</v>
@@ -83606,96 +83609,96 @@
     </row>
     <row r="1635" spans="1:16">
       <c r="A1635" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1635" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1635">
-        <v>2.233911097805582</v>
+        <v>2.374394720592058</v>
       </c>
       <c r="D1635" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1635">
-        <v>2.302337866521036</v>
+        <v>2.388312351428146</v>
       </c>
       <c r="F1635">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1635">
-        <v>0.006926088902194418</v>
+        <v>0.007125605279407942</v>
       </c>
       <c r="H1635">
-        <v>0.007037662133478964</v>
+        <v>0.007011687648571854</v>
       </c>
       <c r="I1635">
-        <v>0.06842676871545361</v>
+        <v>-0.01391763083608843</v>
       </c>
       <c r="J1635">
-        <v>0.5393307821136593</v>
+        <v>0.5326469236340677</v>
       </c>
       <c r="K1635">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1635">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1635">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1635">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1635">
         <v>1</v>
       </c>
       <c r="P1635" t="s">
-        <v>332</v>
+        <v>490</v>
       </c>
     </row>
     <row r="1636" spans="1:16">
       <c r="A1636" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1636" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1636">
-        <v>2.351551250878763</v>
+        <v>2.233911097805582</v>
       </c>
       <c r="D1636" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1636">
-        <v>2.328517789984445</v>
+        <v>2.302337866521036</v>
       </c>
       <c r="F1636">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1636">
-        <v>0.007108448749121238</v>
+        <v>0.006926088902194418</v>
       </c>
       <c r="H1636">
-        <v>0.007031482210015554</v>
+        <v>0.007037662133478964</v>
       </c>
       <c r="I1636">
-        <v>0.02303346089431768</v>
+        <v>0.06842676871545361</v>
       </c>
       <c r="J1636">
         <v>0.5393307821136593</v>
       </c>
       <c r="K1636">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1636">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1636">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1636">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1636">
         <v>1</v>
@@ -83706,46 +83709,46 @@
     </row>
     <row r="1637" spans="1:16">
       <c r="A1637" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1637" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1637">
-        <v>2.34458471177308</v>
+        <v>2.351551250878763</v>
       </c>
       <c r="D1637" t="s">
         <v>336</v>
       </c>
       <c r="E1637">
-        <v>2.328517789984445</v>
+        <v>2.359304405626719</v>
       </c>
       <c r="F1637">
         <v>-1</v>
       </c>
       <c r="G1637">
-        <v>0.007155415288226921</v>
+        <v>0.007108448749121238</v>
       </c>
       <c r="H1637">
-        <v>0.007031482210015554</v>
+        <v>0.007040695594373281</v>
       </c>
       <c r="I1637">
-        <v>0.01606692178863467</v>
+        <v>-0.007753154747956348</v>
       </c>
       <c r="J1637">
         <v>0.5393307821136593</v>
       </c>
       <c r="K1637">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1637">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1637">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1637">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1637">
         <v>1</v>
@@ -83756,96 +83759,96 @@
     </row>
     <row r="1638" spans="1:16">
       <c r="A1638" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1638" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1638">
-        <v>2.20806129043763</v>
+        <v>2.34458471177308</v>
       </c>
       <c r="D1638" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1638">
-        <v>2.276250359774987</v>
+        <v>2.359304405626719</v>
       </c>
       <c r="F1638">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1638">
-        <v>0.00695193870956237</v>
+        <v>0.007155415288226921</v>
       </c>
       <c r="H1638">
-        <v>0.007063749640225013</v>
+        <v>0.007040695594373281</v>
       </c>
       <c r="I1638">
-        <v>0.06818906933735702</v>
+        <v>-0.01471969385363936</v>
       </c>
       <c r="J1638">
-        <v>0.5452732665660622</v>
+        <v>0.5393307821136593</v>
       </c>
       <c r="K1638">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1638">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1638">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1638">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1638">
         <v>1</v>
       </c>
       <c r="P1638" t="s">
-        <v>194</v>
+        <v>332</v>
       </c>
     </row>
     <row r="1639" spans="1:16">
       <c r="A1639" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1639" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1639">
-        <v>2.325344894443666</v>
+        <v>2.20806129043763</v>
       </c>
       <c r="D1639" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1639">
-        <v>2.302608557771968</v>
+        <v>2.276250359774987</v>
       </c>
       <c r="F1639">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1639">
-        <v>0.007134655105556335</v>
+        <v>0.00695193870956237</v>
       </c>
       <c r="H1639">
-        <v>0.007057391442228031</v>
+        <v>0.007063749640225013</v>
       </c>
       <c r="I1639">
-        <v>0.02273633667169772</v>
+        <v>0.06818906933735702</v>
       </c>
       <c r="J1639">
         <v>0.5452732665660622</v>
       </c>
       <c r="K1639">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1639">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1639">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1639">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1639">
         <v>1</v>
@@ -83856,46 +83859,46 @@
     </row>
     <row r="1640" spans="1:16">
       <c r="A1640" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1640" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1640">
-        <v>2.318081231115363</v>
+        <v>2.325344894443666</v>
       </c>
       <c r="D1640" t="s">
         <v>336</v>
       </c>
       <c r="E1640">
-        <v>2.302608557771968</v>
+        <v>2.33351402310329</v>
       </c>
       <c r="F1640">
         <v>-1</v>
       </c>
       <c r="G1640">
-        <v>0.007181918768884637</v>
+        <v>0.007134655105556335</v>
       </c>
       <c r="H1640">
-        <v>0.007057391442228031</v>
+        <v>0.00706648597689671</v>
       </c>
       <c r="I1640">
-        <v>0.01547267334339431</v>
+        <v>-0.008169128659623937</v>
       </c>
       <c r="J1640">
         <v>0.5452732665660622</v>
       </c>
       <c r="K1640">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1640">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1640">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1640">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1640">
         <v>1</v>
@@ -83906,96 +83909,96 @@
     </row>
     <row r="1641" spans="1:16">
       <c r="A1641" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1641" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1641">
-        <v>2.178136022639384</v>
+        <v>2.318081231115363</v>
       </c>
       <c r="D1641" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1641">
-        <v>2.246049917100436</v>
+        <v>2.33351402310329</v>
       </c>
       <c r="F1641">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1641">
-        <v>0.006981863977360617</v>
+        <v>0.007181918768884637</v>
       </c>
       <c r="H1641">
-        <v>0.007093950082899564</v>
+        <v>0.00706648597689671</v>
       </c>
       <c r="I1641">
-        <v>0.06791389446105178</v>
+        <v>-0.01543279198792735</v>
       </c>
       <c r="J1641">
-        <v>0.5521526384737049</v>
+        <v>0.5452732665660622</v>
       </c>
       <c r="K1641">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1641">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1641">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1641">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1641">
         <v>1</v>
       </c>
       <c r="P1641" t="s">
-        <v>491</v>
+        <v>194</v>
       </c>
     </row>
     <row r="1642" spans="1:16">
       <c r="A1642" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1642" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1642">
-        <v>2.295006864330962</v>
+        <v>2.178136022639384</v>
       </c>
       <c r="D1642" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1642">
-        <v>2.272614496254646</v>
+        <v>2.246049917100436</v>
       </c>
       <c r="F1642">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1642">
-        <v>0.00716499313566904</v>
+        <v>0.006981863977360617</v>
       </c>
       <c r="H1642">
-        <v>0.007087385503745353</v>
+        <v>0.007093950082899564</v>
       </c>
       <c r="I1642">
-        <v>0.02239236807631562</v>
+        <v>0.06791389446105178</v>
       </c>
       <c r="J1642">
         <v>0.5521526384737049</v>
       </c>
       <c r="K1642">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1642">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1642">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1642">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1642">
         <v>1</v>
@@ -84006,46 +84009,46 @@
     </row>
     <row r="1643" spans="1:16">
       <c r="A1643" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1643" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1643">
-        <v>2.287399232407276</v>
+        <v>2.295006864330962</v>
       </c>
       <c r="D1643" t="s">
         <v>336</v>
       </c>
       <c r="E1643">
-        <v>2.272614496254646</v>
+        <v>2.303657549024121</v>
       </c>
       <c r="F1643">
         <v>-1</v>
       </c>
       <c r="G1643">
-        <v>0.007212600767592724</v>
+        <v>0.00716499313566904</v>
       </c>
       <c r="H1643">
-        <v>0.007087385503745353</v>
+        <v>0.007096342450975879</v>
       </c>
       <c r="I1643">
-        <v>0.0147847361526301</v>
+        <v>-0.008650684693159327</v>
       </c>
       <c r="J1643">
         <v>0.5521526384737049</v>
       </c>
       <c r="K1643">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1643">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1643">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1643">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1643">
         <v>1</v>
@@ -84056,96 +84059,96 @@
     </row>
     <row r="1644" spans="1:16">
       <c r="A1644" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1644" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1644">
-        <v>2.147989945486611</v>
+        <v>2.287399232407276</v>
       </c>
       <c r="D1644" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1644">
-        <v>2.21562663464051</v>
+        <v>2.303657549024121</v>
       </c>
       <c r="F1644">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1644">
-        <v>0.007012010054513389</v>
+        <v>0.007212600767592724</v>
       </c>
       <c r="H1644">
-        <v>0.00712437336535949</v>
+        <v>0.007096342450975879</v>
       </c>
       <c r="I1644">
-        <v>0.06763668915389953</v>
+        <v>-0.01625831661684485</v>
       </c>
       <c r="J1644">
-        <v>0.5590827711525034</v>
+        <v>0.5521526384737049</v>
       </c>
       <c r="K1644">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1644">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1644">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1644">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1644">
         <v>1</v>
       </c>
       <c r="P1644" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="1645" spans="1:16">
       <c r="A1645" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1645" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1645">
-        <v>2.264444979217461</v>
+        <v>2.147989945486611</v>
       </c>
       <c r="D1645" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1645">
-        <v>2.242399117775085</v>
+        <v>2.21562663464051</v>
       </c>
       <c r="F1645">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1645">
-        <v>0.007195555020782541</v>
+        <v>0.007012010054513389</v>
       </c>
       <c r="H1645">
-        <v>0.007117600882224915</v>
+        <v>0.00712437336535949</v>
       </c>
       <c r="I1645">
-        <v>0.02204586144237597</v>
+        <v>0.06763668915389953</v>
       </c>
       <c r="J1645">
         <v>0.5590827711525034</v>
       </c>
       <c r="K1645">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1645">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1645">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1645">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1645">
         <v>1</v>
@@ -84156,46 +84159,46 @@
     </row>
     <row r="1646" spans="1:16">
       <c r="A1646" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1646" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1646">
-        <v>2.256490840659835</v>
+        <v>2.264444979217461</v>
       </c>
       <c r="D1646" t="s">
         <v>336</v>
       </c>
       <c r="E1646">
-        <v>2.242399117775085</v>
+        <v>2.273580773198136</v>
       </c>
       <c r="F1646">
         <v>-1</v>
       </c>
       <c r="G1646">
-        <v>0.007243509159340166</v>
+        <v>0.007195555020782541</v>
       </c>
       <c r="H1646">
-        <v>0.007117600882224915</v>
+        <v>0.007126419226801865</v>
       </c>
       <c r="I1646">
-        <v>0.01409172288475036</v>
+        <v>-0.0091357939806751</v>
       </c>
       <c r="J1646">
         <v>0.5590827711525034</v>
       </c>
       <c r="K1646">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1646">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1646">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1646">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1646">
         <v>1</v>
@@ -84206,96 +84209,96 @@
     </row>
     <row r="1647" spans="1:16">
       <c r="A1647" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1647" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1647">
-        <v>2.113953665020889</v>
+        <v>2.256490840659835</v>
       </c>
       <c r="D1647" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1647">
-        <v>2.18127737688315</v>
+        <v>2.273580773198136</v>
       </c>
       <c r="F1647">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1647">
-        <v>0.007046046334979112</v>
+        <v>0.007243509159340166</v>
       </c>
       <c r="H1647">
-        <v>0.00715872262311685</v>
+        <v>0.007126419226801865</v>
       </c>
       <c r="I1647">
-        <v>0.06732371186226072</v>
+        <v>-0.01708993253830071</v>
       </c>
       <c r="J1647">
-        <v>0.5669072034434739</v>
+        <v>0.5590827711525034</v>
       </c>
       <c r="K1647">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1647">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1647">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1647">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1647">
         <v>1</v>
       </c>
       <c r="P1647" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="1648" spans="1:16">
       <c r="A1648" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1648" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1648">
-        <v>2.229939232814281</v>
+        <v>2.113953665020889</v>
       </c>
       <c r="D1648" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1648">
-        <v>2.208284592986453</v>
+        <v>2.18127737688315</v>
       </c>
       <c r="F1648">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1648">
-        <v>0.00723006076718572</v>
+        <v>0.007046046334979112</v>
       </c>
       <c r="H1648">
-        <v>0.007151715407013546</v>
+        <v>0.00715872262311685</v>
       </c>
       <c r="I1648">
-        <v>0.02165463982782745</v>
+        <v>0.06732371186226072</v>
       </c>
       <c r="J1648">
         <v>0.5669072034434739</v>
       </c>
       <c r="K1648">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1648">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1648">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1648">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1648">
         <v>1</v>
@@ -84306,46 +84309,46 @@
     </row>
     <row r="1649" spans="1:16">
       <c r="A1649" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1649" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1649">
-        <v>2.221593872642107</v>
+        <v>2.229939232814281</v>
       </c>
       <c r="D1649" t="s">
         <v>336</v>
       </c>
       <c r="E1649">
-        <v>2.208284592986453</v>
+        <v>2.239622737055324</v>
       </c>
       <c r="F1649">
         <v>-1</v>
       </c>
       <c r="G1649">
-        <v>0.007278406127357894</v>
+        <v>0.00723006076718572</v>
       </c>
       <c r="H1649">
-        <v>0.007151715407013546</v>
+        <v>0.007160377262944676</v>
       </c>
       <c r="I1649">
-        <v>0.01330927965565332</v>
+        <v>-0.009683504241043028</v>
       </c>
       <c r="J1649">
         <v>0.5669072034434739</v>
       </c>
       <c r="K1649">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1649">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1649">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1649">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1649">
         <v>1</v>
@@ -84356,96 +84359,96 @@
     </row>
     <row r="1650" spans="1:16">
       <c r="A1650" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1650" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C1650">
-        <v>2.078662048817015</v>
+        <v>2.221593872642107</v>
       </c>
       <c r="D1650" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1650">
-        <v>2.145661240070505</v>
+        <v>2.239622737055324</v>
       </c>
       <c r="F1650">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1650">
-        <v>0.007081337951182986</v>
+        <v>0.007278406127357894</v>
       </c>
       <c r="H1650">
-        <v>0.007194338759929496</v>
+        <v>0.007160377262944676</v>
       </c>
       <c r="I1650">
-        <v>0.06699919125348996</v>
+        <v>-0.01802886441321716</v>
       </c>
       <c r="J1650">
-        <v>0.5750202186627552</v>
+        <v>0.5669072034434739</v>
       </c>
       <c r="K1650">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="L1650">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="M1650">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1650">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1650">
         <v>1</v>
       </c>
       <c r="P1650" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="1651" spans="1:16">
       <c r="A1651" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1651" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1651">
-        <v>2.19416083569725</v>
+        <v>2.078662048817015</v>
       </c>
       <c r="D1651" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1651">
-        <v>2.172911846630387</v>
+        <v>2.145661240070505</v>
       </c>
       <c r="F1651">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1651">
-        <v>0.007265839164302751</v>
+        <v>0.007081337951182986</v>
       </c>
       <c r="H1651">
-        <v>0.007187088153369613</v>
+        <v>0.007194338759929496</v>
       </c>
       <c r="I1651">
-        <v>0.02124898906686301</v>
+        <v>0.06699919125348996</v>
       </c>
       <c r="J1651">
         <v>0.5750202186627552</v>
       </c>
       <c r="K1651">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="L1651">
-        <v>4.73</v>
+        <v>4.58</v>
       </c>
       <c r="M1651">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1651">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1651">
         <v>1</v>
@@ -84456,46 +84459,46 @@
     </row>
     <row r="1652" spans="1:16">
       <c r="A1652" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1652" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1652">
-        <v>2.185409824764112</v>
+        <v>2.19416083569725</v>
       </c>
       <c r="D1652" t="s">
         <v>336</v>
       </c>
       <c r="E1652">
-        <v>2.172911846630387</v>
+        <v>2.204412251003643</v>
       </c>
       <c r="F1652">
         <v>-1</v>
       </c>
       <c r="G1652">
-        <v>0.007314590175235889</v>
+        <v>0.007265839164302751</v>
       </c>
       <c r="H1652">
-        <v>0.007187088153369613</v>
+        <v>0.007195587748996358</v>
       </c>
       <c r="I1652">
-        <v>0.01249797813372489</v>
+        <v>-0.01025141530639306</v>
       </c>
       <c r="J1652">
         <v>0.5750202186627552</v>
       </c>
       <c r="K1652">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1652">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1652">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1652">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1652">
         <v>1</v>
@@ -84506,96 +84509,96 @@
     </row>
     <row r="1653" spans="1:16">
       <c r="A1653" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1653" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C1653">
-        <v>2.152238916147066</v>
+        <v>2.185409824764112</v>
       </c>
       <c r="D1653" t="s">
         <v>336</v>
       </c>
       <c r="E1653">
-        <v>2.131465232290523</v>
+        <v>2.204412251003643</v>
       </c>
       <c r="F1653">
         <v>-1</v>
       </c>
       <c r="G1653">
-        <v>0.007307761083852934</v>
+        <v>0.007314590175235889</v>
       </c>
       <c r="H1653">
-        <v>0.007228534767709477</v>
+        <v>0.007195587748996358</v>
       </c>
       <c r="I1653">
-        <v>0.02077368385654355</v>
+        <v>-0.01900242623953119</v>
       </c>
       <c r="J1653">
-        <v>0.5845263228691461</v>
+        <v>0.5750202186627552</v>
       </c>
       <c r="K1653">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="L1653">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="M1653">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1653">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1653">
         <v>1</v>
       </c>
       <c r="P1653" t="s">
-        <v>195</v>
+        <v>494</v>
       </c>
     </row>
     <row r="1654" spans="1:16">
       <c r="A1654" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1654" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C1654">
-        <v>2.143012600003609</v>
+        <v>2.152238916147066</v>
       </c>
       <c r="D1654" t="s">
         <v>336</v>
       </c>
       <c r="E1654">
-        <v>2.131465232290523</v>
+        <v>2.163155758747906</v>
       </c>
       <c r="F1654">
         <v>-1</v>
       </c>
       <c r="G1654">
-        <v>0.007356987399996392</v>
+        <v>0.007307761083852934</v>
       </c>
       <c r="H1654">
-        <v>0.007228534767709477</v>
+        <v>0.007236844241252094</v>
       </c>
       <c r="I1654">
-        <v>0.01154736771308595</v>
+        <v>-0.01091684260084014</v>
       </c>
       <c r="J1654">
         <v>0.5845263228691461</v>
       </c>
       <c r="K1654">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="L1654">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="M1654">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1654">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1654">
         <v>1</v>
@@ -84606,96 +84609,96 @@
     </row>
     <row r="1655" spans="1:16">
       <c r="A1655" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1655" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C1655">
-        <v>2.120075065382358</v>
+        <v>2.143012600003609</v>
       </c>
       <c r="D1655" t="s">
         <v>336</v>
       </c>
       <c r="E1655">
-        <v>2.099666051035619</v>
+        <v>2.163155758747906</v>
       </c>
       <c r="F1655">
         <v>-1</v>
       </c>
       <c r="G1655">
-        <v>0.007339924934617643</v>
+        <v>0.007356987399996392</v>
       </c>
       <c r="H1655">
-        <v>0.00726033394896438</v>
+        <v>0.007236844241252094</v>
       </c>
       <c r="I1655">
-        <v>0.02040901434673925</v>
+        <v>-0.02014315874429773</v>
       </c>
       <c r="J1655">
-        <v>0.591819713065225</v>
+        <v>0.5845263228691461</v>
       </c>
       <c r="K1655">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="L1655">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="M1655">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1655">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1655">
         <v>1</v>
       </c>
       <c r="P1655" t="s">
-        <v>333</v>
+        <v>195</v>
       </c>
     </row>
     <row r="1656" spans="1:16">
       <c r="A1656" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1656" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C1656">
-        <v>2.110484079729097</v>
+        <v>2.01599326251301</v>
       </c>
       <c r="D1656" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1656">
-        <v>2.099666051035619</v>
+        <v>2.071911459643663</v>
       </c>
       <c r="F1656">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1656">
-        <v>0.007389515920270904</v>
+        <v>0.00722400673748699</v>
       </c>
       <c r="H1656">
-        <v>0.00726033394896438</v>
+        <v>0.007268088540356338</v>
       </c>
       <c r="I1656">
-        <v>0.01081802869347781</v>
+        <v>0.05591819713065282</v>
       </c>
       <c r="J1656">
         <v>0.591819713065225</v>
       </c>
       <c r="K1656">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="L1656">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="M1656">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1656">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1656">
         <v>1</v>
@@ -84706,146 +84709,146 @@
     </row>
     <row r="1657" spans="1:16">
       <c r="A1657" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1657" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C1657">
-        <v>1.984235143612168</v>
+        <v>2.120075065382358</v>
       </c>
       <c r="D1657" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E1657">
-        <v>2.040225518285777</v>
+        <v>2.131502445296924</v>
       </c>
       <c r="F1657">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1657">
-        <v>0.007255764856387832</v>
+        <v>0.007339924934617643</v>
       </c>
       <c r="H1657">
-        <v>0.007299774481714223</v>
+        <v>0.007268497554703077</v>
       </c>
       <c r="I1657">
-        <v>0.05599037467360901</v>
+        <v>-0.01142737991456588</v>
       </c>
       <c r="J1657">
-        <v>0.5990374673608708</v>
+        <v>0.591819713065225</v>
       </c>
       <c r="K1657">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="L1657">
-        <v>4.62</v>
+        <v>4.73</v>
       </c>
       <c r="M1657">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N1657">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="O1657">
         <v>1</v>
       </c>
       <c r="P1657" t="s">
-        <v>495</v>
+        <v>333</v>
       </c>
     </row>
     <row r="1658" spans="1:16">
       <c r="A1658" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1658" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1658">
-        <v>2.08824476893856</v>
+        <v>2.1423204739904</v>
       </c>
       <c r="D1658" t="s">
         <v>336</v>
       </c>
       <c r="E1658">
-        <v>2.068196642306603</v>
+        <v>2.131502445296924</v>
       </c>
       <c r="F1658">
         <v>-1</v>
       </c>
       <c r="G1658">
-        <v>0.007371755231061441</v>
+        <v>0.007397679526009599</v>
       </c>
       <c r="H1658">
-        <v>0.007291803357693397</v>
+        <v>0.007268497554703077</v>
       </c>
       <c r="I1658">
-        <v>0.02004812663195699</v>
+        <v>0.01081802869347648</v>
       </c>
       <c r="J1658">
-        <v>0.5990374673608708</v>
+        <v>0.591819713065225</v>
       </c>
       <c r="K1658">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="L1658">
-        <v>4.73</v>
+        <v>4.77</v>
       </c>
       <c r="M1658">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1658">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1658">
         <v>1</v>
       </c>
       <c r="P1658" t="s">
-        <v>495</v>
+        <v>333</v>
       </c>
     </row>
     <row r="1659" spans="1:16">
       <c r="A1659" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1659" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C1659">
-        <v>2.078292895570516</v>
+        <v>1.984235143612168</v>
       </c>
       <c r="D1659" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E1659">
-        <v>2.068196642306603</v>
+        <v>2.040225518285777</v>
       </c>
       <c r="F1659">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1659">
-        <v>0.007421707104429484</v>
+        <v>0.007255764856387832</v>
       </c>
       <c r="H1659">
-        <v>0.007291803357693397</v>
+        <v>0.007299774481714223</v>
       </c>
       <c r="I1659">
-        <v>0.01009625326391328</v>
+        <v>0.05599037467360901</v>
       </c>
       <c r="J1659">
         <v>0.5990374673608708</v>
       </c>
       <c r="K1659">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="L1659">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="M1659">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N1659">
-        <v>4.68</v>
+        <v>4.67</v>
       </c>
       <c r="O1659">
         <v>1</v>
@@ -84856,143 +84859,143 @@
     </row>
     <row r="1660" spans="1:16">
       <c r="A1660" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1660" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1660">
-        <v>1.894847926243934</v>
+        <v>2.08824476893856</v>
       </c>
       <c r="D1660" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E1660">
-        <v>1.970099980863693</v>
+        <v>2.100177391653821</v>
       </c>
       <c r="F1660">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1660">
-        <v>0.007265152073756067</v>
+        <v>0.007371755231061441</v>
       </c>
       <c r="H1660">
-        <v>0.007389900019136306</v>
+        <v>0.00729982260834618</v>
       </c>
       <c r="I1660">
-        <v>0.07525205461975926</v>
+        <v>-0.01193262271526097</v>
       </c>
       <c r="J1660">
-        <v>0.618698634506006</v>
+        <v>0.5990374673608708</v>
       </c>
       <c r="K1660">
+        <v>4.41</v>
+      </c>
+      <c r="L1660">
+        <v>4.73</v>
+      </c>
+      <c r="M1660">
         <v>4.34</v>
       </c>
-      <c r="L1660">
-        <v>4.58</v>
-      </c>
-      <c r="M1660">
-        <v>4.38</v>
-      </c>
       <c r="N1660">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1660">
         <v>1</v>
       </c>
       <c r="P1660" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1661" spans="1:16">
       <c r="A1661" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1661" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1661">
-        <v>2.001539021828514</v>
+        <v>2.110273644917733</v>
       </c>
       <c r="D1661" t="s">
         <v>336</v>
       </c>
       <c r="E1661">
-        <v>1.982473953553813</v>
+        <v>2.100177391653821</v>
       </c>
       <c r="F1661">
         <v>-1</v>
       </c>
       <c r="G1661">
-        <v>0.007458460978171487</v>
+        <v>0.007429726355082267</v>
       </c>
       <c r="H1661">
-        <v>0.007377526046446186</v>
+        <v>0.00729982260834618</v>
       </c>
       <c r="I1661">
-        <v>0.01906506827470045</v>
+        <v>0.01009625326391195</v>
       </c>
       <c r="J1661">
-        <v>0.618698634506006</v>
+        <v>0.5990374673608708</v>
       </c>
       <c r="K1661">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="L1661">
-        <v>4.73</v>
+        <v>4.77</v>
       </c>
       <c r="M1661">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1661">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1661">
         <v>1</v>
       </c>
       <c r="P1661" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="1662" spans="1:16">
       <c r="A1662" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1662" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1662">
-        <v>2.022978062793332</v>
+        <v>1.894847926243934</v>
       </c>
       <c r="D1662" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E1662">
-        <v>1.982473953553813</v>
+        <v>1.970099980863693</v>
       </c>
       <c r="F1662">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1662">
-        <v>0.007517021937206667</v>
+        <v>0.007265152073756067</v>
       </c>
       <c r="H1662">
-        <v>0.007377526046446186</v>
+        <v>0.007389900019136306</v>
       </c>
       <c r="I1662">
-        <v>0.04050410923951908</v>
+        <v>0.07525205461975926</v>
       </c>
       <c r="J1662">
         <v>0.618698634506006</v>
       </c>
       <c r="K1662">
-        <v>4.44</v>
+        <v>4.34</v>
       </c>
       <c r="L1662">
-        <v>4.77</v>
+        <v>4.58</v>
       </c>
       <c r="M1662">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="N1662">
         <v>4.68</v>
@@ -85006,143 +85009,143 @@
     </row>
     <row r="1663" spans="1:16">
       <c r="A1663" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1663" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1663">
-        <v>1.871971849495402</v>
+        <v>2.001539021828514</v>
       </c>
       <c r="D1663" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E1663">
-        <v>1.947013064698124</v>
+        <v>2.014847926243934</v>
       </c>
       <c r="F1663">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1663">
-        <v>0.007288028150504598</v>
+        <v>0.007458460978171487</v>
       </c>
       <c r="H1663">
-        <v>0.007412986935301875</v>
+        <v>0.007385152073756066</v>
       </c>
       <c r="I1663">
-        <v>0.075041215202722</v>
+        <v>-0.01330890441542021</v>
       </c>
       <c r="J1663">
-        <v>0.6239696199319351</v>
+        <v>0.618698634506006</v>
       </c>
       <c r="K1663">
+        <v>4.41</v>
+      </c>
+      <c r="L1663">
+        <v>4.73</v>
+      </c>
+      <c r="M1663">
         <v>4.34</v>
       </c>
-      <c r="L1663">
-        <v>4.58</v>
-      </c>
-      <c r="M1663">
-        <v>4.38</v>
-      </c>
       <c r="N1663">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1663">
         <v>1</v>
       </c>
       <c r="P1663" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1664" spans="1:16">
       <c r="A1664" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1664" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1664">
-        <v>1.978293976100166</v>
+        <v>2.022978062793332</v>
       </c>
       <c r="D1664" t="s">
         <v>336</v>
       </c>
       <c r="E1664">
-        <v>1.959492457096762</v>
+        <v>2.014847926243934</v>
       </c>
       <c r="F1664">
         <v>-1</v>
       </c>
       <c r="G1664">
-        <v>0.007481706023899835</v>
+        <v>0.007517021937206667</v>
       </c>
       <c r="H1664">
-        <v>0.007400507542903238</v>
+        <v>0.007385152073756066</v>
       </c>
       <c r="I1664">
-        <v>0.0188015190034041</v>
+        <v>0.008130136549398426</v>
       </c>
       <c r="J1664">
-        <v>0.6239696199319351</v>
+        <v>0.618698634506006</v>
       </c>
       <c r="K1664">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="L1664">
-        <v>4.73</v>
+        <v>4.77</v>
       </c>
       <c r="M1664">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1664">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1664">
         <v>1</v>
       </c>
       <c r="P1664" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="1665" spans="1:16">
       <c r="A1665" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1665" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1665">
-        <v>1.999574887502207</v>
+        <v>1.871971849495402</v>
       </c>
       <c r="D1665" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E1665">
-        <v>1.959492457096762</v>
+        <v>1.947013064698124</v>
       </c>
       <c r="F1665">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1665">
-        <v>0.007540425112497791</v>
+        <v>0.007288028150504598</v>
       </c>
       <c r="H1665">
-        <v>0.007400507542903238</v>
+        <v>0.007412986935301875</v>
       </c>
       <c r="I1665">
-        <v>0.04008243040544501</v>
+        <v>0.075041215202722</v>
       </c>
       <c r="J1665">
         <v>0.6239696199319351</v>
       </c>
       <c r="K1665">
-        <v>4.44</v>
+        <v>4.34</v>
       </c>
       <c r="L1665">
-        <v>4.77</v>
+        <v>4.58</v>
       </c>
       <c r="M1665">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="N1665">
         <v>4.68</v>
@@ -85156,43 +85159,43 @@
     </row>
     <row r="1666" spans="1:16">
       <c r="A1666" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1666" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1666">
-        <v>1.855202867366233</v>
+        <v>1.978293976100166</v>
       </c>
       <c r="D1666" t="s">
-        <v>335</v>
+        <v>202</v>
       </c>
       <c r="E1666">
-        <v>1.930089529738272</v>
+        <v>1.934533672299485</v>
       </c>
       <c r="F1666">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1666">
-        <v>0.007304797132633768</v>
+        <v>0.007481706023899835</v>
       </c>
       <c r="H1666">
-        <v>0.007429910470261728</v>
+        <v>0.007425466327700514</v>
       </c>
       <c r="I1666">
-        <v>0.07488666237203878</v>
+        <v>0.0437603038006813</v>
       </c>
       <c r="J1666">
-        <v>0.6278334406990247</v>
+        <v>0.6239696199319351</v>
       </c>
       <c r="K1666">
-        <v>4.34</v>
+        <v>4.41</v>
       </c>
       <c r="L1666">
-        <v>4.58</v>
+        <v>4.73</v>
       </c>
       <c r="M1666">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="N1666">
         <v>4.68</v>
@@ -85201,45 +85204,45 @@
         <v>1</v>
       </c>
       <c r="P1666" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1667" spans="1:16">
       <c r="A1667" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1667" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1667">
-        <v>1.961254526517302</v>
+        <v>1.999574887502207</v>
       </c>
       <c r="D1667" t="s">
         <v>202</v>
       </c>
       <c r="E1667">
-        <v>1.917532860924291</v>
+        <v>1.934533672299485</v>
       </c>
       <c r="F1667">
         <v>-1</v>
       </c>
       <c r="G1667">
-        <v>0.007498745473482699</v>
+        <v>0.007540425112497791</v>
       </c>
       <c r="H1667">
-        <v>0.007442467139075708</v>
+        <v>0.007425466327700514</v>
       </c>
       <c r="I1667">
-        <v>0.04372166559301061</v>
+        <v>0.06504121520272221</v>
       </c>
       <c r="J1667">
-        <v>0.6278334406990247</v>
+        <v>0.6239696199319351</v>
       </c>
       <c r="K1667">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="L1667">
-        <v>4.73</v>
+        <v>4.77</v>
       </c>
       <c r="M1667">
         <v>4.4</v>
@@ -85251,48 +85254,48 @@
         <v>1</v>
       </c>
       <c r="P1667" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1668" spans="1:16">
       <c r="A1668" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1668" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1668">
-        <v>1.98241952329633</v>
+        <v>1.855202867366233</v>
       </c>
       <c r="D1668" t="s">
-        <v>202</v>
+        <v>335</v>
       </c>
       <c r="E1668">
-        <v>1.917532860924291</v>
+        <v>1.930089529738272</v>
       </c>
       <c r="F1668">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1668">
-        <v>0.00755758047670367</v>
+        <v>0.007304797132633768</v>
       </c>
       <c r="H1668">
-        <v>0.007442467139075708</v>
+        <v>0.007429910470261728</v>
       </c>
       <c r="I1668">
-        <v>0.06488666237203855</v>
+        <v>0.07488666237203878</v>
       </c>
       <c r="J1668">
         <v>0.6278334406990247</v>
       </c>
       <c r="K1668">
-        <v>4.44</v>
+        <v>4.34</v>
       </c>
       <c r="L1668">
-        <v>4.77</v>
+        <v>4.58</v>
       </c>
       <c r="M1668">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="N1668">
         <v>4.68</v>
@@ -85306,43 +85309,43 @@
     </row>
     <row r="1669" spans="1:16">
       <c r="A1669" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1669" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1669">
-        <v>1.838673265036769</v>
+        <v>1.961254526517302</v>
       </c>
       <c r="D1669" t="s">
-        <v>335</v>
+        <v>202</v>
       </c>
       <c r="E1669">
-        <v>1.913407580843558</v>
+        <v>1.917532860924291</v>
       </c>
       <c r="F1669">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1669">
-        <v>0.007321326734963232</v>
+        <v>0.007498745473482699</v>
       </c>
       <c r="H1669">
-        <v>0.007446592419156441</v>
+        <v>0.007442467139075708</v>
       </c>
       <c r="I1669">
-        <v>0.07473431580678991</v>
+        <v>0.04372166559301061</v>
       </c>
       <c r="J1669">
-        <v>0.6316421048302377</v>
+        <v>0.6278334406990247</v>
       </c>
       <c r="K1669">
-        <v>4.34</v>
+        <v>4.41</v>
       </c>
       <c r="L1669">
-        <v>4.58</v>
+        <v>4.73</v>
       </c>
       <c r="M1669">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="N1669">
         <v>4.68</v>
@@ -85351,45 +85354,45 @@
         <v>1</v>
       </c>
       <c r="P1669" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1670" spans="1:16">
       <c r="A1670" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1670" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1670">
-        <v>1.944458317698652</v>
+        <v>1.98241952329633</v>
       </c>
       <c r="D1670" t="s">
         <v>202</v>
       </c>
       <c r="E1670">
-        <v>1.900774738746954</v>
+        <v>1.917532860924291</v>
       </c>
       <c r="F1670">
         <v>-1</v>
       </c>
       <c r="G1670">
-        <v>0.007515541682301349</v>
+        <v>0.00755758047670367</v>
       </c>
       <c r="H1670">
-        <v>0.007459225261253046</v>
+        <v>0.007442467139075708</v>
       </c>
       <c r="I1670">
-        <v>0.04368357895169828</v>
+        <v>0.06488666237203855</v>
       </c>
       <c r="J1670">
-        <v>0.6316421048302377</v>
+        <v>0.6278334406990247</v>
       </c>
       <c r="K1670">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="L1670">
-        <v>4.73</v>
+        <v>4.77</v>
       </c>
       <c r="M1670">
         <v>4.4</v>
@@ -85401,48 +85404,48 @@
         <v>1</v>
       </c>
       <c r="P1670" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="1671" spans="1:16">
       <c r="A1671" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1671" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1671">
-        <v>1.965509054553744</v>
+        <v>1.838673265036769</v>
       </c>
       <c r="D1671" t="s">
-        <v>202</v>
+        <v>335</v>
       </c>
       <c r="E1671">
-        <v>1.900774738746954</v>
+        <v>1.913407580843558</v>
       </c>
       <c r="F1671">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1671">
-        <v>0.007574490945446256</v>
+        <v>0.007321326734963232</v>
       </c>
       <c r="H1671">
-        <v>0.007459225261253046</v>
+        <v>0.007446592419156441</v>
       </c>
       <c r="I1671">
-        <v>0.06473431580679012</v>
+        <v>0.07473431580678991</v>
       </c>
       <c r="J1671">
         <v>0.6316421048302377</v>
       </c>
       <c r="K1671">
-        <v>4.44</v>
+        <v>4.34</v>
       </c>
       <c r="L1671">
-        <v>4.77</v>
+        <v>4.58</v>
       </c>
       <c r="M1671">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="N1671">
         <v>4.68</v>
@@ -85456,43 +85459,43 @@
     </row>
     <row r="1672" spans="1:16">
       <c r="A1672" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1672" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C1672">
-        <v>1.822093594109143</v>
+        <v>1.944458317698652</v>
       </c>
       <c r="D1672" t="s">
-        <v>335</v>
+        <v>202</v>
       </c>
       <c r="E1672">
-        <v>1.89667510188895</v>
+        <v>1.900774738746954</v>
       </c>
       <c r="F1672">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1672">
-        <v>0.007337906405890857</v>
+        <v>0.007515541682301349</v>
       </c>
       <c r="H1672">
-        <v>0.007463324898111049</v>
+        <v>0.007459225261253046</v>
       </c>
       <c r="I1672">
-        <v>0.07458150777980777</v>
+        <v>0.04368357895169828</v>
       </c>
       <c r="J1672">
-        <v>0.6354623055048059</v>
+        <v>0.6316421048302377</v>
       </c>
       <c r="K1672">
-        <v>4.34</v>
+        <v>4.41</v>
       </c>
       <c r="L1672">
-        <v>4.58</v>
+        <v>4.73</v>
       </c>
       <c r="M1672">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="N1672">
         <v>4.68</v>
@@ -85501,45 +85504,45 @@
         <v>1</v>
       </c>
       <c r="P1672" t="s">
-        <v>200</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1673" spans="1:16">
       <c r="A1673" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1673" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1673">
-        <v>1.927611232723807</v>
+        <v>1.965509054553744</v>
       </c>
       <c r="D1673" t="s">
         <v>202</v>
       </c>
       <c r="E1673">
-        <v>1.883965855778853</v>
+        <v>1.900774738746954</v>
       </c>
       <c r="F1673">
         <v>-1</v>
       </c>
       <c r="G1673">
-        <v>0.007532388767276194</v>
+        <v>0.007574490945446256</v>
       </c>
       <c r="H1673">
-        <v>0.007476034144221146</v>
+        <v>0.007459225261253046</v>
       </c>
       <c r="I1673">
-        <v>0.04364537694495318</v>
+        <v>0.06473431580679012</v>
       </c>
       <c r="J1673">
-        <v>0.6354623055048059</v>
+        <v>0.6316421048302377</v>
       </c>
       <c r="K1673">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="L1673">
-        <v>4.73</v>
+        <v>4.77</v>
       </c>
       <c r="M1673">
         <v>4.4</v>
@@ -85551,48 +85554,48 @@
         <v>1</v>
       </c>
       <c r="P1673" t="s">
-        <v>200</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1674" spans="1:16">
       <c r="A1674" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1674" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1674">
-        <v>1.948547363558661</v>
+        <v>1.822093594109143</v>
       </c>
       <c r="D1674" t="s">
-        <v>202</v>
+        <v>335</v>
       </c>
       <c r="E1674">
-        <v>1.883965855778853</v>
+        <v>1.89667510188895</v>
       </c>
       <c r="F1674">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1674">
-        <v>0.007591452636441337</v>
+        <v>0.007337906405890857</v>
       </c>
       <c r="H1674">
-        <v>0.007476034144221146</v>
+        <v>0.007463324898111049</v>
       </c>
       <c r="I1674">
-        <v>0.06458150777980798</v>
+        <v>0.07458150777980777</v>
       </c>
       <c r="J1674">
         <v>0.6354623055048059</v>
       </c>
       <c r="K1674">
-        <v>4.44</v>
+        <v>4.34</v>
       </c>
       <c r="L1674">
-        <v>4.77</v>
+        <v>4.58</v>
       </c>
       <c r="M1674">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="N1674">
         <v>4.68</v>
@@ -85606,40 +85609,40 @@
     </row>
     <row r="1675" spans="1:16">
       <c r="A1675" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1675" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1675">
-        <v>1.90949263275245</v>
+        <v>1.948547363558661</v>
       </c>
       <c r="D1675" t="s">
         <v>202</v>
       </c>
       <c r="E1675">
-        <v>1.865888341068203</v>
+        <v>1.883965855778853</v>
       </c>
       <c r="F1675">
         <v>-1</v>
       </c>
       <c r="G1675">
-        <v>0.007550507367247552</v>
+        <v>0.007591452636441337</v>
       </c>
       <c r="H1675">
-        <v>0.007494111658931797</v>
+        <v>0.007476034144221146</v>
       </c>
       <c r="I1675">
-        <v>0.04360429168424673</v>
+        <v>0.06458150777980798</v>
       </c>
       <c r="J1675">
-        <v>0.6395708315754082</v>
+        <v>0.6354623055048059</v>
       </c>
       <c r="K1675">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="L1675">
-        <v>4.73</v>
+        <v>4.77</v>
       </c>
       <c r="M1675">
         <v>4.4</v>
@@ -85651,12 +85654,12 @@
         <v>1</v>
       </c>
       <c r="P1675" t="s">
-        <v>500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="1676" spans="1:16">
       <c r="A1676" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1676" t="s">
         <v>197</v>
@@ -85709,43 +85712,43 @@
         <v>0</v>
       </c>
       <c r="B1677" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C1677">
-        <v>1.891415613485175</v>
+        <v>1.810725711352622</v>
       </c>
       <c r="D1677" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E1677">
-        <v>1.847852312774323</v>
+        <v>1.786472508509219</v>
       </c>
       <c r="F1677">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1677">
-        <v>0.007568584386514827</v>
+        <v>0.007449274288647378</v>
       </c>
       <c r="H1677">
-        <v>0.007512147687225676</v>
+        <v>0.007373527491490781</v>
       </c>
       <c r="I1677">
-        <v>0.04356330071085157</v>
+        <v>-0.02425320284340238</v>
       </c>
       <c r="J1677">
         <v>0.6436699289149265</v>
       </c>
       <c r="K1677">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="L1677">
-        <v>4.73</v>
+        <v>4.63</v>
       </c>
       <c r="M1677">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="N1677">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="O1677">
         <v>1</v>
@@ -85809,43 +85812,43 @@
         <v>0</v>
       </c>
       <c r="B1679" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C1679">
-        <v>1.899471430421895</v>
+        <v>1.798262357037816</v>
       </c>
       <c r="D1679" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E1679">
-        <v>1.835332048165842</v>
+        <v>1.774122974781763</v>
       </c>
       <c r="F1679">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1679">
-        <v>0.007640528569578105</v>
+        <v>0.007461737642962185</v>
       </c>
       <c r="H1679">
-        <v>0.007524667951834157</v>
+        <v>0.007385877025218237</v>
       </c>
       <c r="I1679">
-        <v>0.06413938225605298</v>
+        <v>-0.0241393822560525</v>
       </c>
       <c r="J1679">
         <v>0.6465154435986722</v>
       </c>
       <c r="K1679">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="L1679">
-        <v>4.77</v>
+        <v>4.63</v>
       </c>
       <c r="M1679">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="N1679">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="O1679">
         <v>1</v>
@@ -85856,96 +85859,96 @@
     </row>
     <row r="1680" spans="1:16">
       <c r="A1680" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1680" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C1680">
-        <v>1.784285643587326</v>
+        <v>1.899471430421895</v>
       </c>
       <c r="D1680" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E1680">
-        <v>1.760273902549999</v>
+        <v>1.835332048165842</v>
       </c>
       <c r="F1680">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1680">
-        <v>0.007475714356412673</v>
+        <v>0.007640528569578105</v>
       </c>
       <c r="H1680">
-        <v>0.007399726097450002</v>
+        <v>0.007524667951834157</v>
       </c>
       <c r="I1680">
-        <v>-0.02401174103732684</v>
+        <v>0.06413938225605298</v>
       </c>
       <c r="J1680">
-        <v>0.6497064740668206</v>
+        <v>0.6465154435986722</v>
       </c>
       <c r="K1680">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="L1680">
-        <v>4.63</v>
+        <v>4.77</v>
       </c>
       <c r="M1680">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="N1680">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="O1680">
         <v>1</v>
       </c>
       <c r="P1680" t="s">
-        <v>334</v>
+        <v>501</v>
       </c>
     </row>
     <row r="1681" spans="1:16">
       <c r="A1681" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1681" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C1681">
-        <v>1.885303255143316</v>
+        <v>1.784285643587326</v>
       </c>
       <c r="D1681" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E1681">
-        <v>1.821291514105989</v>
+        <v>1.760273902549999</v>
       </c>
       <c r="F1681">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1681">
-        <v>0.007654696744856683</v>
+        <v>0.007475714356412673</v>
       </c>
       <c r="H1681">
-        <v>0.007538708485894012</v>
+        <v>0.007399726097450002</v>
       </c>
       <c r="I1681">
-        <v>0.06401174103732687</v>
+        <v>-0.02401174103732684</v>
       </c>
       <c r="J1681">
         <v>0.6497064740668206</v>
       </c>
       <c r="K1681">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="L1681">
-        <v>4.77</v>
+        <v>4.63</v>
       </c>
       <c r="M1681">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="N1681">
-        <v>4.68</v>
+        <v>4.58</v>
       </c>
       <c r="O1681">
         <v>1</v>
@@ -85956,34 +85959,34 @@
     </row>
     <row r="1682" spans="1:16">
       <c r="A1682" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1682" t="s">
         <v>197</v>
       </c>
       <c r="C1682">
-        <v>1.867932359194857</v>
+        <v>1.885303255143316</v>
       </c>
       <c r="D1682" t="s">
         <v>202</v>
       </c>
       <c r="E1682">
-        <v>1.804077112715624</v>
+        <v>1.821291514105989</v>
       </c>
       <c r="F1682">
         <v>-1</v>
       </c>
       <c r="G1682">
-        <v>0.007672067640805143</v>
+        <v>0.007654696744856683</v>
       </c>
       <c r="H1682">
-        <v>0.007555922887284376</v>
+        <v>0.007538708485894012</v>
       </c>
       <c r="I1682">
-        <v>0.0638552464792328</v>
+        <v>0.06401174103732687</v>
       </c>
       <c r="J1682">
-        <v>0.6536188380191763</v>
+        <v>0.6497064740668206</v>
       </c>
       <c r="K1682">
         <v>4.44</v>
@@ -86001,7 +86004,7 @@
         <v>1</v>
       </c>
       <c r="P1682" t="s">
-        <v>201</v>
+        <v>334</v>
       </c>
     </row>
     <row r="1683" spans="1:16">
@@ -86012,28 +86015,28 @@
         <v>197</v>
       </c>
       <c r="C1683">
-        <v>1.844100210066407</v>
+        <v>1.867932359194857</v>
       </c>
       <c r="D1683" t="s">
         <v>202</v>
       </c>
       <c r="E1683">
-        <v>1.780459667633377</v>
+        <v>1.804077112715624</v>
       </c>
       <c r="F1683">
         <v>-1</v>
       </c>
       <c r="G1683">
-        <v>0.007695899789933592</v>
+        <v>0.007672067640805143</v>
       </c>
       <c r="H1683">
-        <v>0.007579540332366623</v>
+        <v>0.007555922887284376</v>
       </c>
       <c r="I1683">
-        <v>0.06364054243303041</v>
+        <v>0.0638552464792328</v>
       </c>
       <c r="J1683">
-        <v>0.6589864391742325</v>
+        <v>0.6536188380191763</v>
       </c>
       <c r="K1683">
         <v>4.44</v>
@@ -86051,7 +86054,7 @@
         <v>1</v>
       </c>
       <c r="P1683" t="s">
-        <v>502</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1684" spans="1:16">
@@ -86062,28 +86065,28 @@
         <v>197</v>
       </c>
       <c r="C1684">
-        <v>1.821823028291939</v>
+        <v>1.844100210066407</v>
       </c>
       <c r="D1684" t="s">
         <v>202</v>
       </c>
       <c r="E1684">
-        <v>1.75838318119021</v>
+        <v>1.780459667633377</v>
       </c>
       <c r="F1684">
         <v>-1</v>
       </c>
       <c r="G1684">
-        <v>0.007718176971708061</v>
+        <v>0.007695899789933592</v>
       </c>
       <c r="H1684">
-        <v>0.00760161681880979</v>
+        <v>0.007579540332366623</v>
       </c>
       <c r="I1684">
-        <v>0.06343984710172901</v>
+        <v>0.06364054243303041</v>
       </c>
       <c r="J1684">
-        <v>0.6640038224567704</v>
+        <v>0.6589864391742325</v>
       </c>
       <c r="K1684">
         <v>4.44</v>
@@ -86101,7 +86104,7 @@
         <v>1</v>
       </c>
       <c r="P1684" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="1685" spans="1:16">
@@ -86112,28 +86115,28 @@
         <v>197</v>
       </c>
       <c r="C1685">
-        <v>1.797136409562786</v>
+        <v>1.821823028291939</v>
       </c>
       <c r="D1685" t="s">
         <v>202</v>
       </c>
       <c r="E1685">
-        <v>1.733918964431589</v>
+        <v>1.75838318119021</v>
       </c>
       <c r="F1685">
         <v>-1</v>
       </c>
       <c r="G1685">
-        <v>0.007742863590437214</v>
+        <v>0.007718176971708061</v>
       </c>
       <c r="H1685">
-        <v>0.00762608103556841</v>
+        <v>0.00760161681880979</v>
       </c>
       <c r="I1685">
-        <v>0.0632174451311962</v>
+        <v>0.06343984710172901</v>
       </c>
       <c r="J1685">
-        <v>0.6695638717200932</v>
+        <v>0.6640038224567704</v>
       </c>
       <c r="K1685">
         <v>4.44</v>
@@ -86151,7 +86154,7 @@
         <v>1</v>
       </c>
       <c r="P1685" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="1686" spans="1:16">
@@ -86162,28 +86165,28 @@
         <v>197</v>
       </c>
       <c r="C1686">
-        <v>1.777717943428538</v>
+        <v>1.797136409562786</v>
       </c>
       <c r="D1686" t="s">
         <v>202</v>
       </c>
       <c r="E1686">
-        <v>1.714675439433686</v>
+        <v>1.733918964431589</v>
       </c>
       <c r="F1686">
         <v>-1</v>
       </c>
       <c r="G1686">
-        <v>0.007762282056571462</v>
+        <v>0.007742863590437214</v>
       </c>
       <c r="H1686">
-        <v>0.007645324560566314</v>
+        <v>0.00762608103556841</v>
       </c>
       <c r="I1686">
-        <v>0.06304250399485145</v>
+        <v>0.0632174451311962</v>
       </c>
       <c r="J1686">
-        <v>0.6739374001287076</v>
+        <v>0.6695638717200932</v>
       </c>
       <c r="K1686">
         <v>4.44</v>
@@ -86201,7 +86204,7 @@
         <v>1</v>
       </c>
       <c r="P1686" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="1687" spans="1:16">
@@ -86212,28 +86215,28 @@
         <v>197</v>
       </c>
       <c r="C1687">
-        <v>1.762963563464235</v>
+        <v>1.777717943428538</v>
       </c>
       <c r="D1687" t="s">
         <v>202</v>
       </c>
       <c r="E1687">
-        <v>1.700053981811405</v>
+        <v>1.714675439433686</v>
       </c>
       <c r="F1687">
         <v>-1</v>
       </c>
       <c r="G1687">
-        <v>0.007777036436535764</v>
+        <v>0.007762282056571462</v>
       </c>
       <c r="H1687">
-        <v>0.007659946018188596</v>
+        <v>0.007645324560566314</v>
       </c>
       <c r="I1687">
-        <v>0.06290958165283067</v>
+        <v>0.06304250399485145</v>
       </c>
       <c r="J1687">
-        <v>0.6772604586792261</v>
+        <v>0.6739374001287076</v>
       </c>
       <c r="K1687">
         <v>4.44</v>
@@ -86251,7 +86254,7 @@
         <v>1</v>
       </c>
       <c r="P1687" t="s">
-        <v>196</v>
+        <v>505</v>
       </c>
     </row>
     <row r="1688" spans="1:16">
@@ -86262,28 +86265,28 @@
         <v>197</v>
       </c>
       <c r="C1688">
-        <v>1.746284076491311</v>
+        <v>1.762963563464235</v>
       </c>
       <c r="D1688" t="s">
         <v>202</v>
       </c>
       <c r="E1688">
-        <v>1.683524760486885</v>
+        <v>1.700053981811405</v>
       </c>
       <c r="F1688">
         <v>-1</v>
       </c>
       <c r="G1688">
-        <v>0.007793715923508689</v>
+        <v>0.007777036436535764</v>
       </c>
       <c r="H1688">
-        <v>0.007676475239513115</v>
+        <v>0.007659946018188596</v>
       </c>
       <c r="I1688">
-        <v>0.06275931600442597</v>
+        <v>0.06290958165283067</v>
       </c>
       <c r="J1688">
-        <v>0.6810170998893442</v>
+        <v>0.6772604586792261</v>
       </c>
       <c r="K1688">
         <v>4.44</v>
@@ -86301,7 +86304,7 @@
         <v>1</v>
       </c>
       <c r="P1688" t="s">
-        <v>506</v>
+        <v>196</v>
       </c>
     </row>
     <row r="1689" spans="1:16">
@@ -86312,28 +86315,28 @@
         <v>202</v>
       </c>
       <c r="C1689">
-        <v>1.674871557970142</v>
+        <v>1.683524760486885</v>
       </c>
       <c r="D1689" t="s">
         <v>336</v>
       </c>
       <c r="E1689">
-        <v>1.70219090744314</v>
+        <v>1.744385786480247</v>
       </c>
       <c r="F1689">
         <v>1</v>
       </c>
       <c r="G1689">
-        <v>0.007685128442029858</v>
+        <v>0.007676475239513115</v>
       </c>
       <c r="H1689">
-        <v>0.00765780909255686</v>
+        <v>0.007655614213519754</v>
       </c>
       <c r="I1689">
-        <v>0.02731934947299841</v>
+        <v>0.06086102599336174</v>
       </c>
       <c r="J1689">
-        <v>0.6829837368249677</v>
+        <v>0.6810170998893442</v>
       </c>
       <c r="K1689">
         <v>4.4</v>
@@ -86342,16 +86345,16 @@
         <v>4.68</v>
       </c>
       <c r="M1689">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1689">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1689">
         <v>1</v>
       </c>
       <c r="P1689" t="s">
-        <v>335</v>
+        <v>506</v>
       </c>
     </row>
     <row r="1690" spans="1:16">
@@ -86362,28 +86365,28 @@
         <v>202</v>
       </c>
       <c r="C1690">
-        <v>1.677875252468779</v>
+        <v>1.674871557970142</v>
       </c>
       <c r="D1690" t="s">
         <v>336</v>
       </c>
       <c r="E1690">
-        <v>1.705167295628153</v>
+        <v>1.735850582179641</v>
       </c>
       <c r="F1690">
         <v>1</v>
       </c>
       <c r="G1690">
-        <v>0.007682124747531221</v>
+        <v>0.007685128442029858</v>
       </c>
       <c r="H1690">
-        <v>0.007654832704371847</v>
+        <v>0.00766414941782036</v>
       </c>
       <c r="I1690">
-        <v>0.02729204315937439</v>
+        <v>0.06097902420949897</v>
       </c>
       <c r="J1690">
-        <v>0.6823010789843684</v>
+        <v>0.6829837368249677</v>
       </c>
       <c r="K1690">
         <v>4.4</v>
@@ -86392,16 +86395,16 @@
         <v>4.68</v>
       </c>
       <c r="M1690">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1690">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1690">
         <v>1</v>
       </c>
       <c r="P1690" t="s">
-        <v>507</v>
+        <v>335</v>
       </c>
     </row>
     <row r="1691" spans="1:16">
@@ -86412,28 +86415,28 @@
         <v>202</v>
       </c>
       <c r="C1691">
-        <v>1.68078102647859</v>
+        <v>1.677875252468779</v>
       </c>
       <c r="D1691" t="s">
         <v>336</v>
       </c>
       <c r="E1691">
-        <v>1.708046653510602</v>
+        <v>1.738813317207841</v>
       </c>
       <c r="F1691">
         <v>1</v>
       </c>
       <c r="G1691">
-        <v>0.00767921897352141</v>
+        <v>0.007682124747531221</v>
       </c>
       <c r="H1691">
-        <v>0.007651953346489397</v>
+        <v>0.00766118668279216</v>
       </c>
       <c r="I1691">
-        <v>0.02726562703201285</v>
+        <v>0.06093806473906271</v>
       </c>
       <c r="J1691">
-        <v>0.6816406758003204</v>
+        <v>0.6823010789843684</v>
       </c>
       <c r="K1691">
         <v>4.4</v>
@@ -86442,16 +86445,16 @@
         <v>4.68</v>
       </c>
       <c r="M1691">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1691">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1691">
         <v>1</v>
       </c>
       <c r="P1691" t="s">
-        <v>198</v>
+        <v>507</v>
       </c>
     </row>
     <row r="1692" spans="1:16">
@@ -86462,28 +86465,28 @@
         <v>202</v>
       </c>
       <c r="C1692">
-        <v>1.682618601185694</v>
+        <v>1.68078102647859</v>
       </c>
       <c r="D1692" t="s">
         <v>336</v>
       </c>
       <c r="E1692">
-        <v>1.709867522993096</v>
+        <v>1.74167946702661</v>
       </c>
       <c r="F1692">
         <v>1</v>
       </c>
       <c r="G1692">
-        <v>0.007677381398814306</v>
+        <v>0.00767921897352141</v>
       </c>
       <c r="H1692">
-        <v>0.007650132477006902</v>
+        <v>0.007658320532973391</v>
       </c>
       <c r="I1692">
-        <v>0.02724892180740257</v>
+        <v>0.06089844054802018</v>
       </c>
       <c r="J1692">
-        <v>0.6812230451850695</v>
+        <v>0.6816406758003204</v>
       </c>
       <c r="K1692">
         <v>4.4</v>
@@ -86492,16 +86495,16 @@
         <v>4.68</v>
       </c>
       <c r="M1692">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1692">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1692">
         <v>1</v>
       </c>
       <c r="P1692" t="s">
-        <v>508</v>
+        <v>198</v>
       </c>
     </row>
     <row r="1693" spans="1:16">
@@ -86512,28 +86515,28 @@
         <v>202</v>
       </c>
       <c r="C1693">
-        <v>1.681111718182226</v>
+        <v>1.682618601185694</v>
       </c>
       <c r="D1693" t="s">
         <v>336</v>
       </c>
       <c r="E1693">
-        <v>1.708374338926024</v>
+        <v>1.743491983896799</v>
       </c>
       <c r="F1693">
         <v>1</v>
       </c>
       <c r="G1693">
-        <v>0.007678888281817773</v>
+        <v>0.007677381398814306</v>
       </c>
       <c r="H1693">
-        <v>0.007651625661073976</v>
+        <v>0.007656508016103201</v>
       </c>
       <c r="I1693">
-        <v>0.02726262074379759</v>
+        <v>0.06087338271110498</v>
       </c>
       <c r="J1693">
-        <v>0.6815655185949485</v>
+        <v>0.6812230451850695</v>
       </c>
       <c r="K1693">
         <v>4.4</v>
@@ -86542,16 +86545,16 @@
         <v>4.68</v>
       </c>
       <c r="M1693">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1693">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1693">
         <v>1</v>
       </c>
       <c r="P1693" t="s">
-        <v>199</v>
+        <v>508</v>
       </c>
     </row>
     <row r="1694" spans="1:16">
@@ -86562,28 +86565,28 @@
         <v>202</v>
       </c>
       <c r="C1694">
-        <v>1.67820849236446</v>
+        <v>1.681111718182226</v>
       </c>
       <c r="D1694" t="s">
         <v>336</v>
       </c>
       <c r="E1694">
-        <v>1.705497506070238</v>
+        <v>1.742005649297924</v>
       </c>
       <c r="F1694">
         <v>1</v>
       </c>
       <c r="G1694">
-        <v>0.00768179150763554</v>
+        <v>0.007678888281817773</v>
       </c>
       <c r="H1694">
-        <v>0.007654502493929762</v>
+        <v>0.007657994350702077</v>
       </c>
       <c r="I1694">
-        <v>0.02728901370577752</v>
+        <v>0.06089393111569752</v>
       </c>
       <c r="J1694">
-        <v>0.6822253426444408</v>
+        <v>0.6815655185949485</v>
       </c>
       <c r="K1694">
         <v>4.4</v>
@@ -86592,16 +86595,16 @@
         <v>4.68</v>
       </c>
       <c r="M1694">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1694">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1694">
         <v>1</v>
       </c>
       <c r="P1694" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="1695" spans="1:16">
@@ -86612,28 +86615,28 @@
         <v>202</v>
       </c>
       <c r="C1695">
-        <v>1.675797889944882</v>
+        <v>1.67820849236446</v>
       </c>
       <c r="D1695" t="s">
         <v>336</v>
       </c>
       <c r="E1695">
-        <v>1.70310881821811</v>
+        <v>1.739142012923127</v>
       </c>
       <c r="F1695">
         <v>1</v>
       </c>
       <c r="G1695">
-        <v>0.007684202110055118</v>
+        <v>0.00768179150763554</v>
       </c>
       <c r="H1695">
-        <v>0.007656891181781889</v>
+        <v>0.007660857987076873</v>
       </c>
       <c r="I1695">
-        <v>0.02731092827322845</v>
+        <v>0.06093352055866719</v>
       </c>
       <c r="J1695">
-        <v>0.6827732068307086</v>
+        <v>0.6822253426444408</v>
       </c>
       <c r="K1695">
         <v>4.4</v>
@@ -86642,16 +86645,16 @@
         <v>4.68</v>
       </c>
       <c r="M1695">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1695">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="O1695">
         <v>1</v>
       </c>
       <c r="P1695" t="s">
-        <v>509</v>
+        <v>197</v>
       </c>
     </row>
     <row r="1696" spans="1:16">
@@ -86662,28 +86665,28 @@
         <v>202</v>
       </c>
       <c r="C1696">
-        <v>1.674942783059415</v>
+        <v>1.675797889944882</v>
       </c>
       <c r="D1696" t="s">
         <v>336</v>
       </c>
       <c r="E1696">
-        <v>1.702261485031602</v>
+        <v>1.736764282354725</v>
       </c>
       <c r="F1696">
         <v>1</v>
       </c>
       <c r="G1696">
-        <v>0.007685057216940586</v>
+        <v>0.007684202110055118</v>
       </c>
       <c r="H1696">
-        <v>0.007657738514968397</v>
+        <v>0.007663235717645275</v>
       </c>
       <c r="I1696">
-        <v>0.02731870197218722</v>
+        <v>0.06096639240984336</v>
       </c>
       <c r="J1696">
-        <v>0.6829675493046783</v>
+        <v>0.6827732068307086</v>
       </c>
       <c r="K1696">
         <v>4.4</v>
@@ -86692,16 +86695,116 @@
         <v>4.68</v>
       </c>
       <c r="M1696">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N1696">
+        <v>4.7</v>
+      </c>
+      <c r="O1696">
+        <v>1</v>
+      </c>
+      <c r="P1696" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:16">
+      <c r="A1697" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1697">
+        <v>1.674942783059415</v>
+      </c>
+      <c r="D1697" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1697">
+        <v>1.735920836017697</v>
+      </c>
+      <c r="F1697">
+        <v>1</v>
+      </c>
+      <c r="G1697">
+        <v>0.007685057216940586</v>
+      </c>
+      <c r="H1697">
+        <v>0.007664079163982304</v>
+      </c>
+      <c r="I1697">
+        <v>0.06097805295828174</v>
+      </c>
+      <c r="J1697">
+        <v>0.6829675493046783</v>
+      </c>
+      <c r="K1697">
+        <v>4.4</v>
+      </c>
+      <c r="L1697">
         <v>4.68</v>
       </c>
-      <c r="O1696">
-        <v>1</v>
-      </c>
-      <c r="P1696" t="s">
+      <c r="M1697">
+        <v>4.34</v>
+      </c>
+      <c r="N1697">
+        <v>4.7</v>
+      </c>
+      <c r="O1697">
+        <v>1</v>
+      </c>
+      <c r="P1697" t="s">
         <v>510</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:16">
+      <c r="A1698" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>202</v>
+      </c>
+      <c r="C1698">
+        <v>1.67305987808651</v>
+      </c>
+      <c r="D1698" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1698">
+        <v>1.734063607021695</v>
+      </c>
+      <c r="F1698">
+        <v>1</v>
+      </c>
+      <c r="G1698">
+        <v>0.007686940121913489</v>
+      </c>
+      <c r="H1698">
+        <v>0.007665936392978306</v>
+      </c>
+      <c r="I1698">
+        <v>0.06100372893518458</v>
+      </c>
+      <c r="J1698">
+        <v>0.6833954822530658</v>
+      </c>
+      <c r="K1698">
+        <v>4.4</v>
+      </c>
+      <c r="L1698">
+        <v>4.68</v>
+      </c>
+      <c r="M1698">
+        <v>4.34</v>
+      </c>
+      <c r="N1698">
+        <v>4.7</v>
+      </c>
+      <c r="O1698">
+        <v>1</v>
+      </c>
+      <c r="P1698" t="s">
+        <v>511</v>
       </c>
     </row>
   </sheetData>
